--- a/materials/Convergence card stat excel sheet.xlsx
+++ b/materials/Convergence card stat excel sheet.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="1" r:id="R46e2905169bf4d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relics" sheetId="2" r:id="R78ef6e0b3061448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="3" r:id="R66541e5d5dfa41c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="R406e04dc87394afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="1" r:id="R4ff3da13036949a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relics" sheetId="2" r:id="R660a50aa63bf4fd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="3" r:id="Re7486e469968433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="R49602fe1e1e84cb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1559,7 +1559,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>Escanor "The One"</x:v>
+        <x:v>Escanor</x:v>
       </x:c>
       <x:c r="C28" s="23" t="str">
         <x:f>D28&amp;"/"&amp;E28</x:f>
@@ -4278,7 +4278,7 @@
         <x:v>Latest design</x:v>
       </x:c>
       <x:c r="K97" s="18" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Transformers</x:v>
       </x:c>
       <x:c r="L97" s="17" t="str">
         <x:v>c105</x:v>
@@ -5454,82 +5454,82 @@
         <x:v>c125</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="44" customHeight="1">
+    <x:row r="128" ht="42" customHeight="1">
       <x:c r="A128" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B128" s="14" t="str">
-        <x:v>APR</x:v>
+        <x:v>Dabi</x:v>
       </x:c>
       <x:c r="C128" s="23" t="str">
         <x:f>D128&amp;"/"&amp;E128</x:f>
-        <x:v>0/3</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D128" s="21" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E128" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F128" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G128" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H128" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I128" s="13" t="str">
-        <x:v>Taunt. Passive: After the enemy minion attacks this minion, it can't attack for 2 turns</x:v>
+        <x:v>Battlecry: Deal 1 damage to all other minions</x:v>
       </x:c>
       <x:c r="J128" s="13" t="str">
-        <x:v>Taxes</x:v>
+        <x:v>He burns with anger</x:v>
       </x:c>
       <x:c r="K128" s="13" t="str">
-        <x:v>HxH</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L128" s="12" t="str">
-        <x:v>c135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" ht="42" customHeight="1">
+        <x:v>c129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="44" customHeight="1">
       <x:c r="A129" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B129" s="19" t="str">
-        <x:v>Dabi</x:v>
+        <x:v>Darkwing</x:v>
       </x:c>
       <x:c r="C129" s="24" t="str">
         <x:f>D129&amp;"/"&amp;E129</x:f>
-        <x:v>3/3</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D129" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E129" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F129" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G129" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H129" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I129" s="18" t="str">
-        <x:v>Battlecry: Deal 1 damage to all other minions</x:v>
+        <x:v>Deathrattle: The minion which kills this minion also dies right after</x:v>
       </x:c>
       <x:c r="J129" s="18" t="str">
-        <x:v>He burns with anger</x:v>
+        <x:v>He knew the cost</x:v>
       </x:c>
       <x:c r="K129" s="18" t="str">
-        <x:v>MHA</x:v>
+        <x:v>Invincible</x:v>
       </x:c>
       <x:c r="L129" s="17" t="str">
-        <x:v>c129</x:v>
+        <x:v>c123</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="44" customHeight="1">
@@ -5537,46 +5537,46 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B130" s="14" t="str">
-        <x:v>Darkwing</x:v>
+        <x:v>Giant Crystal</x:v>
       </x:c>
       <x:c r="C130" s="23" t="str">
         <x:f>D130&amp;"/"&amp;E130</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D130" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E130" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F130" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G130" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H130" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I130" s="13" t="str">
-        <x:v>Deathrattle: The minion which kills this minion also dies right after</x:v>
+        <x:v>Divine Shield. Ongoing: Give all other friendly Magic minions +2/+1</x:v>
       </x:c>
       <x:c r="J130" s="13" t="str">
-        <x:v>He knew the cost</x:v>
+        <x:v>Spawnpoint</x:v>
       </x:c>
       <x:c r="K130" s="13" t="str">
-        <x:v>Invincible</x:v>
+        <x:v>Core</x:v>
       </x:c>
       <x:c r="L130" s="12" t="str">
-        <x:v>c123</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" ht="44" customHeight="1">
+        <x:v>c137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="42" customHeight="1">
       <x:c r="A131" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B131" s="19" t="str">
-        <x:v>Giant Crystal</x:v>
+        <x:v>Giant Tree</x:v>
       </x:c>
       <x:c r="C131" s="24" t="str">
         <x:f>D131&amp;"/"&amp;E131</x:f>
@@ -5592,100 +5592,100 @@
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G131" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H131" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I131" s="18" t="str">
-        <x:v>Divine Shield. Ongoing: Give all other friendly Magic minions +2/+1</x:v>
+        <x:v>Passive: All other friendly Nature minions have +2/+1</x:v>
       </x:c>
       <x:c r="J131" s="18" t="str">
-        <x:v>Spawnpoint</x:v>
+        <x:v>Older than the roots it feeds.</x:v>
       </x:c>
       <x:c r="K131" s="18" t="str">
         <x:v>Core</x:v>
       </x:c>
       <x:c r="L131" s="17" t="str">
-        <x:v>c137</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" ht="42" customHeight="1">
+        <x:v>c138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="44" customHeight="1">
       <x:c r="A132" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B132" s="14" t="str">
-        <x:v>Giant Tree</x:v>
+        <x:v>Godrick the Grafted</x:v>
       </x:c>
       <x:c r="C132" s="23" t="str">
         <x:f>D132&amp;"/"&amp;E132</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D132" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E132" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F132" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G132" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H132" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I132" s="13" t="str">
-        <x:v>Passive: All other friendly Nature minions have +2/+1</x:v>
+        <x:v>Battlecry: Destroy a friendly minion to gain its stats and effects</x:v>
       </x:c>
       <x:c r="J132" s="13" t="str">
-        <x:v>Older than the roots it feeds.</x:v>
+        <x:v>Grafted</x:v>
       </x:c>
       <x:c r="K132" s="13" t="str">
-        <x:v>Core</x:v>
+        <x:v>Elden Ring</x:v>
       </x:c>
       <x:c r="L132" s="12" t="str">
-        <x:v>c138</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="44" customHeight="1">
+        <x:v>c130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="42" customHeight="1">
       <x:c r="A133" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B133" s="19" t="str">
-        <x:v>Godrick the Grafted</x:v>
+        <x:v>Gums</x:v>
       </x:c>
       <x:c r="C133" s="24" t="str">
         <x:f>D133&amp;"/"&amp;E133</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D133" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E133" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F133" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G133" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H133" s="24" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I133" s="18" t="str">
-        <x:v>Battlecry: Destroy a friendly minion to gain its stats and effects</x:v>
+        <x:v>Battlecry: Consume an enemy Nature minion with 4 HP or lower</x:v>
       </x:c>
       <x:c r="J133" s="18" t="str">
-        <x:v>Grafted</x:v>
+        <x:v>Insatiable hunger</x:v>
       </x:c>
       <x:c r="K133" s="18" t="str">
-        <x:v>Elden Ring</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L133" s="17" t="str">
-        <x:v>c130</x:v>
+        <x:v>c126</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="42" customHeight="1">
@@ -5693,7 +5693,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B134" s="14" t="str">
-        <x:v>Gums</x:v>
+        <x:v>Illumi</x:v>
       </x:c>
       <x:c r="C134" s="23" t="str">
         <x:f>D134&amp;"/"&amp;E134</x:f>
@@ -5706,25 +5706,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F134" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G134" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H134" s="23" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I134" s="13" t="str">
-        <x:v>Battlecry: Consume an enemy Nature minion with 4 HP or lower</x:v>
+        <x:v>Battlecry: Gain control of a minion with 2 HP or less</x:v>
       </x:c>
       <x:c r="J134" s="13" t="str">
-        <x:v>Insatiable hunger</x:v>
+        <x:v>Control</x:v>
       </x:c>
       <x:c r="K134" s="13" t="str">
-        <x:v>OPM</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L134" s="12" t="str">
-        <x:v>c126</x:v>
+        <x:v>c131</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="42" customHeight="1">
@@ -5732,7 +5732,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B135" s="19" t="str">
-        <x:v>Illumi</x:v>
+        <x:v>Kento Nanami</x:v>
       </x:c>
       <x:c r="C135" s="24" t="str">
         <x:f>D135&amp;"/"&amp;E135</x:f>
@@ -5751,27 +5751,27 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H135" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I135" s="18" t="str">
-        <x:v>Battlecry: Gain control of a minion with 2 HP or less</x:v>
+        <x:v>Battlecry: Set an enemy minion's HP to 1</x:v>
       </x:c>
       <x:c r="J135" s="18" t="str">
-        <x:v>Control</x:v>
+        <x:v>7:3 Ratio Technique</x:v>
       </x:c>
       <x:c r="K135" s="18" t="str">
-        <x:v>HxH</x:v>
+        <x:v>Jujutsu Kaisen</x:v>
       </x:c>
       <x:c r="L135" s="17" t="str">
-        <x:v>c131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" ht="42" customHeight="1">
+        <x:v>c132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="60" customHeight="1">
       <x:c r="A136" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B136" s="14" t="str">
-        <x:v>Kento Nanami</x:v>
+        <x:v>Knov</x:v>
       </x:c>
       <x:c r="C136" s="23" t="str">
         <x:f>D136&amp;"/"&amp;E136</x:f>
@@ -5784,7 +5784,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F136" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G136" s="23" t="str">
         <x:v>Magic</x:v>
@@ -5793,37 +5793,37 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I136" s="13" t="str">
-        <x:v>Battlecry: Set an enemy minion's HP to 1</x:v>
+        <x:v>Battlecry: Choose a friendly and an enemy minion to place in the pocket room, removing them from the board. After 2 turns, return the minion with the higher ATK</x:v>
       </x:c>
       <x:c r="J136" s="13" t="str">
-        <x:v>7:3 Ratio Technique</x:v>
+        <x:v>The Room</x:v>
       </x:c>
       <x:c r="K136" s="13" t="str">
-        <x:v>Jujutsu Kaisen</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L136" s="12" t="str">
-        <x:v>c132</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="60" customHeight="1">
+        <x:v>c124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="44" customHeight="1">
       <x:c r="A137" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B137" s="19" t="str">
-        <x:v>Knov</x:v>
+        <x:v>Knuckle</x:v>
       </x:c>
       <x:c r="C137" s="24" t="str">
         <x:f>D137&amp;"/"&amp;E137</x:f>
-        <x:v>1/1</x:v>
+        <x:v>0/3</x:v>
       </x:c>
       <x:c r="D137" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E137" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F137" s="24" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G137" s="24" t="str">
         <x:v>Magic</x:v>
@@ -5832,16 +5832,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I137" s="18" t="str">
-        <x:v>Battlecry: Choose a friendly and an enemy minion to place in the pocket room, removing them from the board. After 2 turns, return the minion with the higher ATK</x:v>
+        <x:v>Taunt. Passive: After the enemy minion attacks this minion, it can't attack for 2 turns</x:v>
       </x:c>
       <x:c r="J137" s="18" t="str">
-        <x:v>The Room</x:v>
+        <x:v>Taxes</x:v>
       </x:c>
       <x:c r="K137" s="18" t="str">
         <x:v>HxH</x:v>
       </x:c>
       <x:c r="L137" s="17" t="str">
-        <x:v>c124</x:v>
+        <x:v>c135</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="44" customHeight="1">
@@ -5888,38 +5888,38 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B139" s="19" t="str">
-        <x:v>Margit the Fell Omen</x:v>
+        <x:v>Modern Tank</x:v>
       </x:c>
       <x:c r="C139" s="24" t="str">
         <x:f>D139&amp;"/"&amp;E139</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D139" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E139" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F139" s="24" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G139" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H139" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I139" s="18" t="str">
-        <x:v>Deathrattle: Summon Morgott, the Omen King (3/3)</x:v>
+        <x:v>Battlecry: Deal 1 damage to an enemy minion</x:v>
       </x:c>
       <x:c r="J139" s="18" t="str">
-        <x:v>The immovable</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K139" s="18" t="str">
-        <x:v>Elden Ring</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L139" s="17" t="str">
-        <x:v>c155</x:v>
+        <x:v>c139</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="42" customHeight="1">
@@ -5927,38 +5927,38 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B140" s="14" t="str">
-        <x:v>Modern Tank</x:v>
+        <x:v>Morgott, the Omen King</x:v>
       </x:c>
       <x:c r="C140" s="23" t="str">
         <x:f>D140&amp;"/"&amp;E140</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D140" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E140" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F140" s="23" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G140" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H140" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I140" s="13" t="str">
-        <x:v>Battlecry: Deal 1 damage to an enemy minion</x:v>
+        <x:v>Taunt. Battlecry: Summon Margit (1/1 with Taunt)</x:v>
       </x:c>
       <x:c r="J140" s="13" t="str">
-        <x:v>-</x:v>
+        <x:v>The immovable</x:v>
       </x:c>
       <x:c r="K140" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Elden Ring</x:v>
       </x:c>
       <x:c r="L140" s="12" t="str">
-        <x:v>c139</x:v>
+        <x:v>c155</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="42" customHeight="1">
@@ -6228,7 +6228,7 @@
         <x:v>Preparation beats power.</x:v>
       </x:c>
       <x:c r="K147" s="18" t="str">
-        <x:v>DCU</x:v>
+        <x:v>DCEU</x:v>
       </x:c>
       <x:c r="L147" s="17" t="str">
         <x:v>c005</x:v>
@@ -7658,7 +7658,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926dd1d12fe64f49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a408c53735046e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8378,7 +8378,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03a016a13e3f48db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d90fcead2b43f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/materials/Convergence card stat excel sheet.xlsx
+++ b/materials/Convergence card stat excel sheet.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="1" r:id="R4ff3da13036949a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relics" sheetId="2" r:id="R660a50aa63bf4fd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="3" r:id="Re7486e469968433e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="R49602fe1e1e84cb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="1" r:id="Ra05350dfdec84dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relics" sheetId="2" r:id="Rfa2cc636fc694db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="3" r:id="R6db6af589ee54aa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" r:id="R570376a03dac4569"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardRoster" displayName="CardRoster" ref="A1:L183" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardRoster" displayName="CardRoster" ref="A1:L185" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Cost"/>
     <x:tableColumn id="2" name="Name"/>
@@ -651,7 +651,7 @@
         <x:v>Transcended</x:v>
       </x:c>
       <x:c r="K4" s="13" t="str">
-        <x:v>DCU</x:v>
+        <x:v>Watchmen</x:v>
       </x:c>
       <x:c r="L4" s="12" t="str">
         <x:v>c043</x:v>
@@ -774,43 +774,43 @@
         <x:v>c044</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+    <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="21" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Neo</x:v>
+        <x:v>Rick Prime</x:v>
       </x:c>
       <x:c r="C8" s="23" t="str">
         <x:f>D8&amp;"/"&amp;E8</x:f>
-        <x:v>5/7</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D8" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="21" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F8" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G8" s="23" t="str">
         <x:v>Tech</x:v>
       </x:c>
       <x:c r="H8" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I8" s="13" t="str">
-        <x:v>Battlecry: Choose a friendly minion board slot. Minions on that slot cannot be Silenced, Frozen, or Chained</x:v>
+        <x:v>Battlecry: Return all other minions to their owners' hands</x:v>
       </x:c>
       <x:c r="J8" s="13" t="str">
-        <x:v>He decided the bullets were harmless.</x:v>
+        <x:v>What…</x:v>
       </x:c>
       <x:c r="K8" s="13" t="str">
-        <x:v>Matrix</x:v>
+        <x:v>Rick and Morty</x:v>
       </x:c>
       <x:c r="L8" s="12" t="str">
-        <x:v>c026</x:v>
+        <x:v>c045</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -818,155 +818,155 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="19" t="str">
-        <x:v>Rick Prime</x:v>
+        <x:v>Saitama</x:v>
       </x:c>
       <x:c r="C9" s="24" t="str">
         <x:f>D9&amp;"/"&amp;E9</x:f>
-        <x:v>1/1</x:v>
+        <x:v>10/10</x:v>
       </x:c>
       <x:c r="D9" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G9" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H9" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I9" s="18" t="str">
-        <x:v>Battlecry: Return all other minions to their owners' hands</x:v>
+        <x:v>Passive: Ignores ATK damage less than 5</x:v>
       </x:c>
       <x:c r="J9" s="18" t="str">
-        <x:v>What…</x:v>
+        <x:v>The punchline is always the same.</x:v>
       </x:c>
       <x:c r="K9" s="18" t="str">
-        <x:v>Rick and Morty</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L9" s="17" t="str">
-        <x:v>c045</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+        <x:v>c025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="21" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>Saitama</x:v>
+        <x:v>Thanos</x:v>
       </x:c>
       <x:c r="C10" s="23" t="str">
         <x:f>D10&amp;"/"&amp;E10</x:f>
-        <x:v>10/10</x:v>
+        <x:v>9/10</x:v>
       </x:c>
       <x:c r="D10" s="21" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E10" s="21" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F10" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G10" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H10" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I10" s="13" t="str">
-        <x:v>Passive: Ignores ATK damage less than 5</x:v>
+        <x:v>Battlecry: Each player destroys a random other minion and discards a random card</x:v>
       </x:c>
       <x:c r="J10" s="13" t="str">
-        <x:v>The punchline is always the same.</x:v>
+        <x:v>Balance. At any cost.</x:v>
       </x:c>
       <x:c r="K10" s="13" t="str">
-        <x:v>OPM</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L10" s="12" t="str">
-        <x:v>c025</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="44" customHeight="1">
+        <x:v>c027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="22" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:v>Thanos</x:v>
+        <x:v>The Watcher</x:v>
       </x:c>
       <x:c r="C11" s="24" t="str">
         <x:f>D11&amp;"/"&amp;E11</x:f>
-        <x:v>9/10</x:v>
+        <x:v>10/7</x:v>
       </x:c>
       <x:c r="D11" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F11" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G11" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H11" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I11" s="18" t="str">
-        <x:v>Battlecry: Each player destroys a random other minion and discards a random card</x:v>
+        <x:v>Cannot attack. Passive: Your opponent's hand is revealed to you</x:v>
       </x:c>
       <x:c r="J11" s="18" t="str">
-        <x:v>Balance. At any cost.</x:v>
+        <x:v>The Witness</x:v>
       </x:c>
       <x:c r="K11" s="18" t="str">
         <x:v>MCU</x:v>
       </x:c>
       <x:c r="L11" s="17" t="str">
-        <x:v>c027</x:v>
+        <x:v>c046</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="21" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>The Watcher</x:v>
+        <x:v>Ainz Ooal Gown</x:v>
       </x:c>
       <x:c r="C12" s="23" t="str">
         <x:f>D12&amp;"/"&amp;E12</x:f>
-        <x:v>10/7</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D12" s="21" t="n">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E12" s="21" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F12" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G12" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H12" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I12" s="13" t="str">
-        <x:v>Cannot attack. Passive: Your opponent's hand is revealed to you</x:v>
+        <x:v>Battlecry: Set all enemy minions' HP to 1</x:v>
       </x:c>
       <x:c r="J12" s="13" t="str">
-        <x:v>The Witness</x:v>
+        <x:v>The king of death.</x:v>
       </x:c>
       <x:c r="K12" s="13" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Overlord</x:v>
       </x:c>
       <x:c r="L12" s="12" t="str">
-        <x:v>c046</x:v>
+        <x:v>c023</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
@@ -974,20 +974,20 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="19" t="str">
-        <x:v>Ainz Ooal Gown</x:v>
+        <x:v>Aizen</x:v>
       </x:c>
       <x:c r="C13" s="24" t="str">
         <x:f>D13&amp;"/"&amp;E13</x:f>
-        <x:v>3/3</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D13" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E13" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F13" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G13" s="24" t="str">
         <x:v>Magic</x:v>
@@ -996,16 +996,16 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I13" s="18" t="str">
-        <x:v>Battlecry: Set all enemy minions' HP to 1</x:v>
+        <x:v>Reborn twice. Silence and chain your killer</x:v>
       </x:c>
       <x:c r="J13" s="18" t="str">
-        <x:v>The king of death.</x:v>
+        <x:v>All part of the plan</x:v>
       </x:c>
       <x:c r="K13" s="18" t="str">
-        <x:v>Overlord</x:v>
+        <x:v>Bleach</x:v>
       </x:c>
       <x:c r="L13" s="17" t="str">
-        <x:v>c023</x:v>
+        <x:v>c050</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
@@ -1013,38 +1013,38 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>Aizen</x:v>
+        <x:v>Antimatter Bomb</x:v>
       </x:c>
       <x:c r="C14" s="23" t="str">
         <x:f>D14&amp;"/"&amp;E14</x:f>
-        <x:v>4/4</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D14" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G14" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H14" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I14" s="13" t="str">
-        <x:v>Reborn twice. Silence and chain your killer</x:v>
+        <x:v>Deathrattle: Deal 20 damage to both cores</x:v>
       </x:c>
       <x:c r="J14" s="13" t="str">
-        <x:v>All part of the plan</x:v>
+        <x:v>No safe distance.</x:v>
       </x:c>
       <x:c r="K14" s="13" t="str">
-        <x:v>Bleach</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L14" s="12" t="str">
-        <x:v>c050</x:v>
+        <x:v>c186</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
@@ -1086,51 +1086,51 @@
         <x:v>c051</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="42" customHeight="1">
+    <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="21" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>Conquest</x:v>
+        <x:v>Death Star</x:v>
       </x:c>
       <x:c r="C16" s="23" t="str">
         <x:f>D16&amp;"/"&amp;E16</x:f>
-        <x:v>6/6</x:v>
+        <x:v>7/6</x:v>
       </x:c>
       <x:c r="D16" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E16" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F16" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G16" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H16" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I16" s="13" t="str">
-        <x:v>Ongoing: Gain +2/+2 for each enemy Good minion</x:v>
+        <x:v>Battlecry: Mark an enemy minion or the enemy core. At the start of your next turn, if Death Star survives, destroy the marked minion or deal 12 damage to the marked core</x:v>
       </x:c>
       <x:c r="J16" s="13" t="str">
-        <x:v>Named after his purpose.</x:v>
+        <x:v>The ultimate weapon.</x:v>
       </x:c>
       <x:c r="K16" s="13" t="str">
-        <x:v>Invincible</x:v>
+        <x:v>Star Wars</x:v>
       </x:c>
       <x:c r="L16" s="12" t="str">
-        <x:v>c024</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="60" customHeight="1">
+        <x:v>c055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="44" customHeight="1">
       <x:c r="A17" s="22" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B17" s="19" t="str">
-        <x:v>Death Star</x:v>
+        <x:v>Doomsday</x:v>
       </x:c>
       <x:c r="C17" s="24" t="str">
         <x:f>D17&amp;"/"&amp;E17</x:f>
@@ -1146,22 +1146,22 @@
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G17" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H17" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I17" s="18" t="str">
-        <x:v>Battlecry: Mark an enemy minion or the enemy core. At the start of your next turn, if Death Star survives, destroy the marked minion or deal 12 damage to the marked core</x:v>
+        <x:v>Passive: After it is attacked, gain immunity to that enemies Camp type of attack for the next 3 enemy turns</x:v>
       </x:c>
       <x:c r="J17" s="18" t="str">
-        <x:v>The ultimate weapon.</x:v>
+        <x:v>Death is his only teacher, and he has learned well</x:v>
       </x:c>
       <x:c r="K17" s="18" t="str">
-        <x:v>Star Wars</x:v>
+        <x:v>DCU</x:v>
       </x:c>
       <x:c r="L17" s="17" t="str">
-        <x:v>c055</x:v>
+        <x:v>c056</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="44" customHeight="1">
@@ -1169,38 +1169,38 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>Doomsday</x:v>
+        <x:v>Dormammu</x:v>
       </x:c>
       <x:c r="C18" s="23" t="str">
         <x:f>D18&amp;"/"&amp;E18</x:f>
-        <x:v>7/6</x:v>
+        <x:v>8/5</x:v>
       </x:c>
       <x:c r="D18" s="21" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F18" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G18" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H18" s="23" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I18" s="13" t="str">
-        <x:v>Passive: After it is attacked, gain immunity to that enemies Camp type of attack for the next 3 enemy turns</x:v>
+        <x:v>Battlecry: Choose an enemy minion. Banish it to the Dark Dimension until Dormammu dies</x:v>
       </x:c>
       <x:c r="J18" s="13" t="str">
-        <x:v>Death is his only teacher, and he has learned well</x:v>
+        <x:v>I've come to bargain</x:v>
       </x:c>
       <x:c r="K18" s="13" t="str">
-        <x:v>DCU</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L18" s="12" t="str">
-        <x:v>c056</x:v>
+        <x:v>c052</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="44" customHeight="1">
@@ -1208,38 +1208,38 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B19" s="19" t="str">
-        <x:v>Dormammu</x:v>
+        <x:v>Gojo</x:v>
       </x:c>
       <x:c r="C19" s="24" t="str">
         <x:f>D19&amp;"/"&amp;E19</x:f>
-        <x:v>8/5</x:v>
+        <x:v>4/8</x:v>
       </x:c>
       <x:c r="D19" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" s="22" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E19" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="F19" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G19" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H19" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I19" s="18" t="str">
-        <x:v>Battlecry: Choose an enemy minion. Banish it to the Dark Dimension until Dormammu dies</x:v>
+        <x:v>Passive: All enemy minions are temporarily silenced (until Gojo dies)</x:v>
       </x:c>
       <x:c r="J19" s="18" t="str">
-        <x:v>I've come to bargain</x:v>
+        <x:v>Infinity is rude.</x:v>
       </x:c>
       <x:c r="K19" s="18" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Jujutsu Kaisen</x:v>
       </x:c>
       <x:c r="L19" s="17" t="str">
-        <x:v>c052</x:v>
+        <x:v>c022</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="44" customHeight="1">
@@ -1247,20 +1247,20 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>Gojo</x:v>
+        <x:v>Mob Psycho</x:v>
       </x:c>
       <x:c r="C20" s="23" t="str">
         <x:f>D20&amp;"/"&amp;E20</x:f>
-        <x:v>4/8</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D20" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G20" s="23" t="str">
         <x:v>Magic</x:v>
@@ -1269,37 +1269,37 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I20" s="13" t="str">
-        <x:v>Passive: All enemy minions are temporarily silenced (until Gojo dies)</x:v>
+        <x:v>Battlecry: If 3 or more friendly minions are on the board, return them to your hand and set Mob's stats to 12/12</x:v>
       </x:c>
       <x:c r="J20" s="13" t="str">
-        <x:v>Infinity is rude.</x:v>
+        <x:v>A quiet storm</x:v>
       </x:c>
       <x:c r="K20" s="13" t="str">
-        <x:v>Jujutsu Kaisen</x:v>
+        <x:v>Mob Psycho</x:v>
       </x:c>
       <x:c r="L20" s="12" t="str">
-        <x:v>c022</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="44" customHeight="1">
+        <x:v>c053</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="22" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B21" s="19" t="str">
-        <x:v>Mob Psycho</x:v>
+        <x:v>Rimuru Tempest</x:v>
       </x:c>
       <x:c r="C21" s="24" t="str">
         <x:f>D21&amp;"/"&amp;E21</x:f>
-        <x:v>5/5</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D21" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E21" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F21" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G21" s="24" t="str">
         <x:v>Magic</x:v>
@@ -1308,55 +1308,55 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I21" s="18" t="str">
-        <x:v>Battlecry: If 3 or more friendly minions are on the board, return them to your hand and set Mob's stats to 12/12</x:v>
+        <x:v>Battlecry: Destroy a minion. Gain its stats. Ongoing: Gain +1/+1</x:v>
       </x:c>
       <x:c r="J21" s="18" t="str">
-        <x:v>A quiet storm</x:v>
+        <x:v>Infinite growth</x:v>
       </x:c>
       <x:c r="K21" s="18" t="str">
-        <x:v>Mob Psycho</x:v>
+        <x:v>Tensura</x:v>
       </x:c>
       <x:c r="L21" s="17" t="str">
-        <x:v>c053</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="42" customHeight="1">
+        <x:v>c049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="44" customHeight="1">
       <x:c r="A22" s="21" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Planetary Defense Grid</x:v>
+        <x:v>Ten Tails</x:v>
       </x:c>
       <x:c r="C22" s="23" t="str">
         <x:f>D22&amp;"/"&amp;E22</x:f>
-        <x:v>4/8</x:v>
+        <x:v>7/5</x:v>
       </x:c>
       <x:c r="D22" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E22" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="23" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G22" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H22" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I22" s="13" t="str">
-        <x:v>Taunt. Passive: All other Taunt minions have +2/+2</x:v>
+        <x:v>Battlecry: Chain all other minions</x:v>
       </x:c>
       <x:c r="J22" s="13" t="str">
-        <x:v>The shield watches from orbit.</x:v>
+        <x:v>The beast before beginnings, hungry for the end</x:v>
       </x:c>
       <x:c r="K22" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Naruto</x:v>
       </x:c>
       <x:c r="L22" s="12" t="str">
-        <x:v>c177</x:v>
+        <x:v>c057</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
@@ -1364,59 +1364,59 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B23" s="19" t="str">
-        <x:v>Rimuru Tempest</x:v>
+        <x:v>The 7 Heroic Spirits</x:v>
       </x:c>
       <x:c r="C23" s="24" t="str">
         <x:f>D23&amp;"/"&amp;E23</x:f>
-        <x:v>1/1</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D23" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E23" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F23" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G23" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H23" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I23" s="18" t="str">
-        <x:v>Battlecry: Destroy a minion. Gain its stats. Ongoing: Gain +1/+1</x:v>
+        <x:v>Battlecry: All your other minions gain a random Ascension Relic</x:v>
       </x:c>
       <x:c r="J23" s="18" t="str">
-        <x:v>Infinite growth</x:v>
+        <x:v>Legends reborn</x:v>
       </x:c>
       <x:c r="K23" s="18" t="str">
-        <x:v>Tensura</x:v>
+        <x:v>Fate</x:v>
       </x:c>
       <x:c r="L23" s="17" t="str">
-        <x:v>c049</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="44" customHeight="1">
+        <x:v>c101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="21" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>Ten Tails</x:v>
+        <x:v>Conquest</x:v>
       </x:c>
       <x:c r="C24" s="23" t="str">
         <x:f>D24&amp;"/"&amp;E24</x:f>
-        <x:v>7/5</x:v>
+        <x:v>6/6</x:v>
       </x:c>
       <x:c r="D24" s="21" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E24" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F24" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G24" s="23" t="str">
         <x:v>Nature</x:v>
@@ -1425,55 +1425,55 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I24" s="13" t="str">
-        <x:v>Battlecry: Chain all other minions</x:v>
+        <x:v>Ongoing: Gain +2/+2 for each enemy Good minion</x:v>
       </x:c>
       <x:c r="J24" s="13" t="str">
-        <x:v>The beast before beginnings, hungry for the end</x:v>
+        <x:v>Named after his purpose.</x:v>
       </x:c>
       <x:c r="K24" s="13" t="str">
-        <x:v>Naruto</x:v>
+        <x:v>Invincible</x:v>
       </x:c>
       <x:c r="L24" s="12" t="str">
-        <x:v>c057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="42" customHeight="1">
+        <x:v>c024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="44" customHeight="1">
       <x:c r="A25" s="22" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="19" t="str">
-        <x:v>Chaos</x:v>
+        <x:v>Doom Slayer</x:v>
       </x:c>
       <x:c r="C25" s="24" t="str">
         <x:f>D25&amp;"/"&amp;E25</x:f>
-        <x:v>4/4</x:v>
+        <x:v>3/8</x:v>
       </x:c>
       <x:c r="D25" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E25" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F25" s="24" t="str">
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G25" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H25" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I25" s="18" t="str">
-        <x:v>Battlecry: Summon a random minion from the deck</x:v>
+        <x:v>Passive: Deal triple damage to Evil minions. Whenever Doom Slayer kills an Evil minion, heal him for 3 HP</x:v>
       </x:c>
       <x:c r="J25" s="18" t="str">
-        <x:v>He gives gifts. He never mentions the cost</x:v>
+        <x:v>He cleaned Hell and came back.</x:v>
       </x:c>
       <x:c r="K25" s="18" t="str">
-        <x:v>Hades</x:v>
+        <x:v>Doom</x:v>
       </x:c>
       <x:c r="L25" s="17" t="str">
-        <x:v>c061</x:v>
+        <x:v>c016</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
@@ -1481,38 +1481,38 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>Cthulhu</x:v>
+        <x:v>Escanor</x:v>
       </x:c>
       <x:c r="C26" s="23" t="str">
         <x:f>D26&amp;"/"&amp;E26</x:f>
-        <x:v>8/8</x:v>
+        <x:v>8/4</x:v>
       </x:c>
       <x:c r="D26" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E26" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F26" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G26" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H26" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I26" s="13" t="str">
-        <x:v>Chained. Passive: Immune to Tech minions</x:v>
+        <x:v>Battlecry: Double your other friendly minions attack</x:v>
       </x:c>
       <x:c r="J26" s="13" t="str">
-        <x:v>He dreams</x:v>
+        <x:v>The Sun, incarnated</x:v>
       </x:c>
       <x:c r="K26" s="13" t="str">
-        <x:v>Myth</x:v>
+        <x:v>Seven Deadly Sins</x:v>
       </x:c>
       <x:c r="L26" s="12" t="str">
-        <x:v>c136</x:v>
+        <x:v>c047</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="44" customHeight="1">
@@ -1520,38 +1520,38 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="19" t="str">
-        <x:v>Doom Slayer</x:v>
+        <x:v>Floor Guardians</x:v>
       </x:c>
       <x:c r="C27" s="24" t="str">
         <x:f>D27&amp;"/"&amp;E27</x:f>
-        <x:v>3/8</x:v>
+        <x:v>6/6</x:v>
       </x:c>
       <x:c r="D27" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E27" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F27" s="24" t="str">
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G27" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H27" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I27" s="18" t="str">
-        <x:v>Passive: Deal triple damage to Evil minions. Whenever Doom Slayer kills an Evil minion, heal him for 3 HP</x:v>
+        <x:v>Battlecry: Choose 1 friendly minion board slot. Minions on that board slot gain +1/+1 at the start of your turn</x:v>
       </x:c>
       <x:c r="J27" s="18" t="str">
-        <x:v>He cleaned Hell and came back.</x:v>
+        <x:v>They do not guard the floors—they own them</x:v>
       </x:c>
       <x:c r="K27" s="18" t="str">
-        <x:v>Doom</x:v>
+        <x:v>Overlord</x:v>
       </x:c>
       <x:c r="L27" s="17" t="str">
-        <x:v>c016</x:v>
+        <x:v>c083</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
@@ -1559,38 +1559,38 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>Escanor</x:v>
+        <x:v>Gilgamesh</x:v>
       </x:c>
       <x:c r="C28" s="23" t="str">
         <x:f>D28&amp;"/"&amp;E28</x:f>
-        <x:v>8/4</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D28" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E28" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F28" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G28" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H28" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I28" s="13" t="str">
-        <x:v>Battlecry: Double your other friendly minions attack</x:v>
+        <x:v>Battlecry: Equip a random Ascension Relic</x:v>
       </x:c>
       <x:c r="J28" s="13" t="str">
-        <x:v>The Sun, incarnated</x:v>
+        <x:v>Unworthy.</x:v>
       </x:c>
       <x:c r="K28" s="13" t="str">
-        <x:v>Seven Deadly Sins</x:v>
+        <x:v>Fate</x:v>
       </x:c>
       <x:c r="L28" s="12" t="str">
-        <x:v>c047</x:v>
+        <x:v>c019</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
@@ -1598,38 +1598,38 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="19" t="str">
-        <x:v>Gilgamesh</x:v>
+        <x:v>Gol D. Roger</x:v>
       </x:c>
       <x:c r="C29" s="24" t="str">
         <x:f>D29&amp;"/"&amp;E29</x:f>
-        <x:v>5/5</x:v>
+        <x:v>6/5</x:v>
       </x:c>
       <x:c r="D29" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E29" s="22" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F29" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G29" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H29" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I29" s="18" t="str">
-        <x:v>Battlecry: Equip a random Ascension Relic</x:v>
+        <x:v>Battlecry: Choose 1 of 3 Ascension Relics. Add it to your hand</x:v>
       </x:c>
       <x:c r="J29" s="18" t="str">
-        <x:v>Unworthy.</x:v>
+        <x:v>He has already won.</x:v>
       </x:c>
       <x:c r="K29" s="18" t="str">
-        <x:v>Fate</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L29" s="17" t="str">
-        <x:v>c019</x:v>
+        <x:v>c017</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
@@ -1637,56 +1637,56 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>Gol D. Roger</x:v>
+        <x:v>Kaido</x:v>
       </x:c>
       <x:c r="C30" s="23" t="str">
         <x:f>D30&amp;"/"&amp;E30</x:f>
-        <x:v>6/5</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D30" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E30" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F30" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G30" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H30" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I30" s="13" t="str">
-        <x:v>Battlecry: Choose 1 of 3 Ascension Relics. Add it to your hand</x:v>
+        <x:v>Battlecry: Destroy an enemy Taunt minion</x:v>
       </x:c>
       <x:c r="J30" s="13" t="str">
-        <x:v>He has already won.</x:v>
+        <x:v>Rules of the seas</x:v>
       </x:c>
       <x:c r="K30" s="13" t="str">
         <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L30" s="12" t="str">
-        <x:v>c017</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="42" customHeight="1">
+        <x:v>c058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="44" customHeight="1">
       <x:c r="A31" s="22" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="19" t="str">
-        <x:v>Kaido</x:v>
+        <x:v>Korosensei</x:v>
       </x:c>
       <x:c r="C31" s="24" t="str">
         <x:f>D31&amp;"/"&amp;E31</x:f>
-        <x:v>5/5</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D31" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E31" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F31" s="24" t="str">
         <x:v>Legendary</x:v>
@@ -1695,58 +1695,58 @@
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H31" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I31" s="18" t="str">
-        <x:v>Battlecry: Destroy an enemy Taunt minion</x:v>
+        <x:v>Passive: Evade 20% of attacks. Can only be damaged by ATK of 4 and higher</x:v>
       </x:c>
       <x:c r="J31" s="18" t="str">
-        <x:v>Rules of the seas</x:v>
+        <x:v>Mach 20</x:v>
       </x:c>
       <x:c r="K31" s="18" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>Assasination Classroom</x:v>
       </x:c>
       <x:c r="L31" s="17" t="str">
-        <x:v>c058</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="44" customHeight="1">
+        <x:v>c059</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Korosensei</x:v>
+        <x:v>Marshall D. Teach</x:v>
       </x:c>
       <x:c r="C32" s="23" t="str">
         <x:f>D32&amp;"/"&amp;E32</x:f>
-        <x:v>4/4</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D32" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E32" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F32" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G32" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H32" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I32" s="13" t="str">
-        <x:v>Passive: Evade 20% of attacks. Can only be damaged by ATK of 4 and higher</x:v>
+        <x:v>Ongoing: Copy a passive from 1 friendly and 1 enemy minion</x:v>
       </x:c>
       <x:c r="J32" s="13" t="str">
-        <x:v>Mach 20</x:v>
+        <x:v>Steal steal steal.</x:v>
       </x:c>
       <x:c r="K32" s="13" t="str">
-        <x:v>Assasination Classroom</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L32" s="12" t="str">
-        <x:v>c059</x:v>
+        <x:v>c018</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
@@ -1754,215 +1754,215 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="19" t="str">
-        <x:v>Lelouch Lamperouge</x:v>
+        <x:v>Meteor</x:v>
       </x:c>
       <x:c r="C33" s="24" t="str">
         <x:f>D33&amp;"/"&amp;E33</x:f>
-        <x:v>1/1</x:v>
+        <x:v>4/3</x:v>
       </x:c>
       <x:c r="D33" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E33" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F33" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G33" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H33" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I33" s="18" t="str">
-        <x:v>Battlecry: Gain control of an enemy minion</x:v>
+        <x:v>Battlecry: Deal 4 damage to all other minions</x:v>
       </x:c>
       <x:c r="J33" s="18" t="str">
-        <x:v>Obey</x:v>
+        <x:v>It was never going to miss.</x:v>
       </x:c>
       <x:c r="K33" s="18" t="str">
-        <x:v>Code Geass</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L33" s="17" t="str">
-        <x:v>c048</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="42" customHeight="1">
+        <x:v>c176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="44" customHeight="1">
       <x:c r="A34" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>Light Yagami</x:v>
+        <x:v>Monkey D. Luffy</x:v>
       </x:c>
       <x:c r="C34" s="23" t="str">
         <x:f>D34&amp;"/"&amp;E34</x:f>
-        <x:v>4/3</x:v>
+        <x:v>6/4</x:v>
       </x:c>
       <x:c r="D34" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E34" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F34" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G34" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H34" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I34" s="13" t="str">
-        <x:v>Battlecry: Destroy an enemy Nature minion</x:v>
+        <x:v>Battlecry: Free all friendly Chained minions. They may attack immediately and gain Divine Shield</x:v>
       </x:c>
       <x:c r="J34" s="13" t="str">
-        <x:v>Ryuk, come help.</x:v>
+        <x:v>Reality bends; laughter reigns</x:v>
       </x:c>
       <x:c r="K34" s="13" t="str">
-        <x:v>Death Note</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L34" s="12" t="str">
-        <x:v>c021</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="42" customHeight="1">
+        <x:v>c060</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="44" customHeight="1">
       <x:c r="A35" s="22" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="19" t="str">
-        <x:v>Marshall D. Teach</x:v>
+        <x:v>Naruto</x:v>
       </x:c>
       <x:c r="C35" s="24" t="str">
         <x:f>D35&amp;"/"&amp;E35</x:f>
-        <x:v>5/5</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D35" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E35" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F35" s="24" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G35" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H35" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I35" s="18" t="str">
-        <x:v>Ongoing: Copy a passive from 1 friendly and 1 enemy minion</x:v>
+        <x:v>Battlecry: Fill your board with 2/2 Shadow Clones in empty friendly slots</x:v>
       </x:c>
       <x:c r="J35" s="18" t="str">
-        <x:v>Steal steal steal.</x:v>
+        <x:v>A thousand bodies, one will.</x:v>
       </x:c>
       <x:c r="K35" s="18" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>Naruto</x:v>
       </x:c>
       <x:c r="L35" s="17" t="str">
-        <x:v>c018</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="42" customHeight="1">
+        <x:v>c183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="44" customHeight="1">
       <x:c r="A36" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
-        <x:v>Meteor</x:v>
+        <x:v>Neo</x:v>
       </x:c>
       <x:c r="C36" s="23" t="str">
         <x:f>D36&amp;"/"&amp;E36</x:f>
-        <x:v>4/3</x:v>
+        <x:v>6/6</x:v>
       </x:c>
       <x:c r="D36" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E36" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F36" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G36" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H36" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I36" s="13" t="str">
-        <x:v>Battlecry: Deal 4 damage to all other minions</x:v>
+        <x:v>Battlecry: Choose a friendly minion board slot. Minions on that slot cannot be Silenced, Frozen, or Chained</x:v>
       </x:c>
       <x:c r="J36" s="13" t="str">
-        <x:v>It was never going to miss.</x:v>
+        <x:v>He decided the bullets were harmless.</x:v>
       </x:c>
       <x:c r="K36" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Matrix</x:v>
       </x:c>
       <x:c r="L36" s="12" t="str">
-        <x:v>c176</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="44" customHeight="1">
+        <x:v>c026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="22" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="19" t="str">
-        <x:v>Monkey D. Luffy</x:v>
+        <x:v>S-Class Heroes</x:v>
       </x:c>
       <x:c r="C37" s="24" t="str">
         <x:f>D37&amp;"/"&amp;E37</x:f>
-        <x:v>6/4</x:v>
+        <x:v>4/7</x:v>
       </x:c>
       <x:c r="D37" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E37" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F37" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G37" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>ALL</x:v>
       </x:c>
       <x:c r="H37" s="24" t="str">
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I37" s="18" t="str">
-        <x:v>Battlecry: Free all friendly Chained minions. They may attack immediately and gain Divine Shield</x:v>
+        <x:v>Ongoing: Give +2/+2 to all Good minions</x:v>
       </x:c>
       <x:c r="J37" s="18" t="str">
-        <x:v>Reality bends; laughter reigns</x:v>
+        <x:v>The strongest team</x:v>
       </x:c>
       <x:c r="K37" s="18" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L37" s="17" t="str">
-        <x:v>c060</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="44" customHeight="1">
+        <x:v>c062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="60" customHeight="1">
       <x:c r="A38" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
-        <x:v>Naruto</x:v>
+        <x:v>Seven Deadly Sins</x:v>
       </x:c>
       <x:c r="C38" s="23" t="str">
         <x:f>D38&amp;"/"&amp;E38</x:f>
-        <x:v>2/2</x:v>
+        <x:v>4/5</x:v>
       </x:c>
       <x:c r="D38" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E38" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F38" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G38" s="23" t="str">
         <x:v>Magic</x:v>
@@ -1971,16 +1971,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I38" s="13" t="str">
-        <x:v>Battlecry: Fill your board with 2/2 Shadow Clones in empty friendly slots</x:v>
+        <x:v>Battlecry: Fill your empty slots with 1/1 Sin minions. Each enters with a different keyword at random: Taunt, Divine Shield, Charge, Chained</x:v>
       </x:c>
       <x:c r="J38" s="13" t="str">
-        <x:v>A thousand bodies, one will.</x:v>
+        <x:v>The Magic Number</x:v>
       </x:c>
       <x:c r="K38" s="13" t="str">
-        <x:v>Naruto</x:v>
+        <x:v>Seven Deadly Sins</x:v>
       </x:c>
       <x:c r="L38" s="12" t="str">
-        <x:v>c183</x:v>
+        <x:v>c064</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
@@ -1988,56 +1988,56 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="19" t="str">
-        <x:v>S-Class Heroes</x:v>
+        <x:v>Superman</x:v>
       </x:c>
       <x:c r="C39" s="24" t="str">
         <x:f>D39&amp;"/"&amp;E39</x:f>
-        <x:v>4/7</x:v>
+        <x:v>6/6</x:v>
       </x:c>
       <x:c r="D39" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E39" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F39" s="24" t="str">
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G39" s="24" t="str">
-        <x:v>ALL</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H39" s="24" t="str">
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I39" s="18" t="str">
-        <x:v>Ongoing: Give +2/+2 to all Good minions</x:v>
+        <x:v>Passive: Friendly Good minions cannot lose more than 3 HP at once</x:v>
       </x:c>
       <x:c r="J39" s="18" t="str">
-        <x:v>The strongest team</x:v>
+        <x:v>The heir's son rises.</x:v>
       </x:c>
       <x:c r="K39" s="18" t="str">
-        <x:v>OPM</x:v>
+        <x:v>DCU</x:v>
       </x:c>
       <x:c r="L39" s="17" t="str">
-        <x:v>c062</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="60" customHeight="1">
+        <x:v>c020</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="21" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
-        <x:v>Seven Deadly Sins</x:v>
+        <x:v>Whitebeard</x:v>
       </x:c>
       <x:c r="C40" s="23" t="str">
         <x:f>D40&amp;"/"&amp;E40</x:f>
-        <x:v>4/5</x:v>
+        <x:v>4/3</x:v>
       </x:c>
       <x:c r="D40" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E40" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F40" s="23" t="str">
         <x:v>Epic</x:v>
@@ -2046,76 +2046,76 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H40" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I40" s="13" t="str">
-        <x:v>Battlecry: Fill your empty slots with 1/1 Sin minions. Each enters with a different keyword at random: Taunt, Divine Shield, Charge, Chained</x:v>
+        <x:v>Battlecry: Deal 3 damage to all enemy minions</x:v>
       </x:c>
       <x:c r="J40" s="13" t="str">
-        <x:v>The Magic Number</x:v>
+        <x:v>Split the World in two</x:v>
       </x:c>
       <x:c r="K40" s="13" t="str">
-        <x:v>Seven Deadly Sins</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L40" s="12" t="str">
-        <x:v>c064</x:v>
+        <x:v>c065</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="19" t="str">
-        <x:v>Superman</x:v>
+        <x:v>All for One</x:v>
       </x:c>
       <x:c r="C41" s="24" t="str">
         <x:f>D41&amp;"/"&amp;E41</x:f>
-        <x:v>6/6</x:v>
+        <x:v>4/5</x:v>
       </x:c>
       <x:c r="D41" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E41" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F41" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G41" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H41" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I41" s="18" t="str">
-        <x:v>Passive: Friendly Good minions cannot lose more than 3 HP at once</x:v>
+        <x:v>Passive: Copy and enact the Passive of every enemy minion</x:v>
       </x:c>
       <x:c r="J41" s="18" t="str">
-        <x:v>The heir's son rises.</x:v>
+        <x:v>A Collector</x:v>
       </x:c>
       <x:c r="K41" s="18" t="str">
-        <x:v>DCU</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L41" s="17" t="str">
-        <x:v>c020</x:v>
+        <x:v>c071</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
-        <x:v>Whitebeard</x:v>
+        <x:v>All Might</x:v>
       </x:c>
       <x:c r="C42" s="23" t="str">
         <x:f>D42&amp;"/"&amp;E42</x:f>
-        <x:v>4/3</x:v>
+        <x:v>4/5</x:v>
       </x:c>
       <x:c r="D42" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E42" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F42" s="23" t="str">
         <x:v>Epic</x:v>
@@ -2124,19 +2124,19 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H42" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I42" s="13" t="str">
-        <x:v>Battlecry: Deal 3 damage to all enemy minions</x:v>
+        <x:v>Passive: While on the board, every enemy minion has -2 ATK</x:v>
       </x:c>
       <x:c r="J42" s="13" t="str">
-        <x:v>Split the World in two</x:v>
+        <x:v>Number One</x:v>
       </x:c>
       <x:c r="K42" s="13" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L42" s="12" t="str">
-        <x:v>c065</x:v>
+        <x:v>c073</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
@@ -2144,59 +2144,59 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="19" t="str">
-        <x:v>Aladdin Lamp</x:v>
+        <x:v>Avengers</x:v>
       </x:c>
       <x:c r="C43" s="24" t="str">
         <x:f>D43&amp;"/"&amp;E43</x:f>
-        <x:v>5/4</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D43" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E43" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F43" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G43" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>ALL</x:v>
       </x:c>
       <x:c r="H43" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I43" s="18" t="str">
-        <x:v>Battlecry: Make a wish</x:v>
+        <x:v>Passive: Invulnerable as long as you control another Good minion</x:v>
       </x:c>
       <x:c r="J43" s="18" t="str">
-        <x:v>What does thy wish</x:v>
+        <x:v>When the board breaks, they assemble.</x:v>
       </x:c>
       <x:c r="K43" s="18" t="str">
-        <x:v>Aladdin</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L43" s="17" t="str">
-        <x:v>c072</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="42" customHeight="1">
+        <x:v>c015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="44" customHeight="1">
       <x:c r="A44" s="21" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
-        <x:v>All for One</x:v>
+        <x:v>Big Mom</x:v>
       </x:c>
       <x:c r="C44" s="23" t="str">
         <x:f>D44&amp;"/"&amp;E44</x:f>
-        <x:v>4/5</x:v>
+        <x:v>6/6</x:v>
       </x:c>
       <x:c r="D44" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E44" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F44" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G44" s="23" t="str">
         <x:v>Magic</x:v>
@@ -2205,37 +2205,37 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I44" s="13" t="str">
-        <x:v>Passive: Copy and enact the Passive of every enemy minion</x:v>
+        <x:v>Battlecry: Destroy a friendly minion. Gain its ATK and HP, in addition to your own</x:v>
       </x:c>
       <x:c r="J44" s="13" t="str">
-        <x:v>A Collector</x:v>
+        <x:v>Greed</x:v>
       </x:c>
       <x:c r="K44" s="13" t="str">
-        <x:v>MHA</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L44" s="12" t="str">
-        <x:v>c071</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="42" customHeight="1">
+        <x:v>c098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="44" customHeight="1">
       <x:c r="A45" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B45" s="19" t="str">
-        <x:v>All Might</x:v>
+        <x:v>Doctor Strange</x:v>
       </x:c>
       <x:c r="C45" s="24" t="str">
         <x:f>D45&amp;"/"&amp;E45</x:f>
-        <x:v>4/5</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D45" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E45" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F45" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G45" s="24" t="str">
         <x:v>Magic</x:v>
@@ -2244,16 +2244,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I45" s="18" t="str">
-        <x:v>Passive: While on the board, every enemy minion has -2 ATK</x:v>
+        <x:v>Battlecry: Offer a bargain. Your opponent chooses: lose 10 Core HP, lose a random minion, or lose 5 mana next turn</x:v>
       </x:c>
       <x:c r="J45" s="18" t="str">
-        <x:v>Number One</x:v>
+        <x:v>Magic trumps everything.</x:v>
       </x:c>
       <x:c r="K45" s="18" t="str">
-        <x:v>MHA</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L45" s="17" t="str">
-        <x:v>c073</x:v>
+        <x:v>c013</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
@@ -2261,38 +2261,38 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
-        <x:v>Avengers</x:v>
+        <x:v>Elder Centipede</x:v>
       </x:c>
       <x:c r="C46" s="23" t="str">
         <x:f>D46&amp;"/"&amp;E46</x:f>
-        <x:v>4/4</x:v>
+        <x:v>5/6</x:v>
       </x:c>
       <x:c r="D46" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E46" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F46" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G46" s="23" t="str">
-        <x:v>ALL</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H46" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I46" s="13" t="str">
-        <x:v>Passive: Invulnerable as long as you control another Good minion</x:v>
+        <x:v>Ongoing: Gain +2/+2</x:v>
       </x:c>
       <x:c r="J46" s="13" t="str">
-        <x:v>When the board breaks, they assemble.</x:v>
+        <x:v>Billion year old</x:v>
       </x:c>
       <x:c r="K46" s="13" t="str">
-        <x:v>MCU</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L46" s="12" t="str">
-        <x:v>c015</x:v>
+        <x:v>c066</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="44" customHeight="1">
@@ -2300,38 +2300,38 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="19" t="str">
-        <x:v>Doctor Strange</x:v>
+        <x:v>G-Man</x:v>
       </x:c>
       <x:c r="C47" s="24" t="str">
         <x:f>D47&amp;"/"&amp;E47</x:f>
-        <x:v>3/3</x:v>
+        <x:v>3/6</x:v>
       </x:c>
       <x:c r="D47" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E47" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F47" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G47" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H47" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I47" s="18" t="str">
-        <x:v>Battlecry: Offer a bargain. Your opponent chooses: lose 10 Core HP, lose a random minion, or lose 5 mana next turn</x:v>
+        <x:v>Battlecry: Put an enemy minion into stasis - remove it from the board for 2 turns</x:v>
       </x:c>
       <x:c r="J47" s="18" t="str">
-        <x:v>Magic trumps everything.</x:v>
+        <x:v>Time, Mr. Freeman.</x:v>
       </x:c>
       <x:c r="K47" s="18" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Half-Life</x:v>
       </x:c>
       <x:c r="L47" s="17" t="str">
-        <x:v>c013</x:v>
+        <x:v>c012</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
@@ -2339,137 +2339,137 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
-        <x:v>Elder Centipede</x:v>
+        <x:v>Genie</x:v>
       </x:c>
       <x:c r="C48" s="23" t="str">
         <x:f>D48&amp;"/"&amp;E48</x:f>
-        <x:v>5/6</x:v>
+        <x:v>5/4</x:v>
       </x:c>
       <x:c r="D48" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E48" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F48" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G48" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H48" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I48" s="13" t="str">
-        <x:v>Ongoing: Gain +2/+2</x:v>
+        <x:v>Battlecry: Make a wish</x:v>
       </x:c>
       <x:c r="J48" s="13" t="str">
-        <x:v>Billion year old</x:v>
+        <x:v>What does thy wish</x:v>
       </x:c>
       <x:c r="K48" s="13" t="str">
-        <x:v>OPM</x:v>
+        <x:v>Aladdin</x:v>
       </x:c>
       <x:c r="L48" s="12" t="str">
-        <x:v>c066</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="44" customHeight="1">
+        <x:v>c072</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B49" s="19" t="str">
-        <x:v>G-Man</x:v>
+        <x:v>Godzilla</x:v>
       </x:c>
       <x:c r="C49" s="24" t="str">
         <x:f>D49&amp;"/"&amp;E49</x:f>
-        <x:v>3/6</x:v>
+        <x:v>4/5</x:v>
       </x:c>
       <x:c r="D49" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E49" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F49" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G49" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H49" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I49" s="18" t="str">
-        <x:v>Battlecry: Put an enemy minion into stasis - remove it from the board for 2 turns</x:v>
+        <x:v>Passive: Deal 2 damage to all enemies each time you take damage</x:v>
       </x:c>
       <x:c r="J49" s="18" t="str">
-        <x:v>Time, Mr. Freeman.</x:v>
+        <x:v>Laser breathing</x:v>
       </x:c>
       <x:c r="K49" s="18" t="str">
-        <x:v>Half-Life</x:v>
+        <x:v>Godzilla</x:v>
       </x:c>
       <x:c r="L49" s="17" t="str">
-        <x:v>c012</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="42" customHeight="1">
+        <x:v>c076</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="44" customHeight="1">
       <x:c r="A50" s="21" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
-        <x:v>Godzilla</x:v>
+        <x:v>Grand Master Yoda</x:v>
       </x:c>
       <x:c r="C50" s="23" t="str">
         <x:f>D50&amp;"/"&amp;E50</x:f>
-        <x:v>4/5</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D50" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E50" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F50" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G50" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H50" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I50" s="13" t="str">
-        <x:v>Passive: Deal 2 damage to all enemies each time you take damage</x:v>
+        <x:v>Cannot attack. Ongoing: Your lowest-ATK friendly minion gains +2/+2</x:v>
       </x:c>
       <x:c r="J50" s="13" t="str">
-        <x:v>Laser breathing</x:v>
+        <x:v>Nine centuries of learning</x:v>
       </x:c>
       <x:c r="K50" s="13" t="str">
-        <x:v>Godzilla</x:v>
+        <x:v>Star Wars</x:v>
       </x:c>
       <x:c r="L50" s="12" t="str">
-        <x:v>c076</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="44" customHeight="1">
+        <x:v>c074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="19" t="str">
-        <x:v>Grand Master Yoda</x:v>
+        <x:v>Isaac Netero</x:v>
       </x:c>
       <x:c r="C51" s="24" t="str">
         <x:f>D51&amp;"/"&amp;E51</x:f>
-        <x:v>5/5</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D51" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E51" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F51" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G51" s="24" t="str">
         <x:v>Magic</x:v>
@@ -2478,16 +2478,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I51" s="18" t="str">
-        <x:v>Cannot attack. Ongoing: Your lowest-ATK friendly minion gains +2/+2</x:v>
+        <x:v>Divine Shield. Deathrattle: Deal 3 damage to all enemy minions</x:v>
       </x:c>
       <x:c r="J51" s="18" t="str">
-        <x:v>Nine centuries of learning</x:v>
+        <x:v>Each prayer strikes harder than any fist</x:v>
       </x:c>
       <x:c r="K51" s="18" t="str">
-        <x:v>Star Wars</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L51" s="17" t="str">
-        <x:v>c074</x:v>
+        <x:v>c069</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
@@ -2495,7 +2495,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>Isaac Netero</x:v>
+        <x:v>Kizaru</x:v>
       </x:c>
       <x:c r="C52" s="23" t="str">
         <x:f>D52&amp;"/"&amp;E52</x:f>
@@ -2508,103 +2508,103 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F52" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G52" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H52" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I52" s="13" t="str">
-        <x:v>Divine Shield. Deathrattle: Deal 3 damage to all enemy minions</x:v>
+        <x:v>Divine Shield. Ongoing: Gain Divine Shield</x:v>
       </x:c>
       <x:c r="J52" s="13" t="str">
-        <x:v>Each prayer strikes harder than any fist</x:v>
+        <x:v>Light logic.</x:v>
       </x:c>
       <x:c r="K52" s="13" t="str">
-        <x:v>HxH</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L52" s="12" t="str">
-        <x:v>c069</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="44" customHeight="1">
+        <x:v>c014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="19" t="str">
-        <x:v>King</x:v>
+        <x:v>Lelouch Lamperouge</x:v>
       </x:c>
       <x:c r="C53" s="24" t="str">
         <x:f>D53&amp;"/"&amp;E53</x:f>
-        <x:v>0/7</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D53" s="22" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E53" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F53" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G53" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H53" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I53" s="18" t="str">
-        <x:v>Cannot attack. Passive: At the start of each enemy turn, a random enemy minion is Attack Locked for that turn</x:v>
+        <x:v>Battlecry: Gain control of an enemy minion</x:v>
       </x:c>
       <x:c r="J53" s="18" t="str">
-        <x:v>Luckiest man alive</x:v>
+        <x:v>Obey</x:v>
       </x:c>
       <x:c r="K53" s="18" t="str">
-        <x:v>OPM</x:v>
+        <x:v>Code Geass</x:v>
       </x:c>
       <x:c r="L53" s="17" t="str">
-        <x:v>c077</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="42" customHeight="1">
+        <x:v>c048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="44" customHeight="1">
       <x:c r="A54" s="21" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
-        <x:v>Kizaru</x:v>
+        <x:v>Meruem</x:v>
       </x:c>
       <x:c r="C54" s="23" t="str">
         <x:f>D54&amp;"/"&amp;E54</x:f>
-        <x:v>4/4</x:v>
+        <x:v>4/6</x:v>
       </x:c>
       <x:c r="D54" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E54" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F54" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G54" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H54" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I54" s="13" t="str">
-        <x:v>Divine Shield. Ongoing: Gain Divine Shield</x:v>
+        <x:v>Passive: Whenever Meruem kills a minion, gain +1/+1 and gain its effects</x:v>
       </x:c>
       <x:c r="J54" s="13" t="str">
-        <x:v>Light logic.</x:v>
+        <x:v>Loyalty</x:v>
       </x:c>
       <x:c r="K54" s="13" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L54" s="12" t="str">
-        <x:v>c014</x:v>
+        <x:v>c084</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
@@ -2612,38 +2612,38 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="19" t="str">
-        <x:v>Silver Surfer</x:v>
+        <x:v>Planetary Defense Grid</x:v>
       </x:c>
       <x:c r="C55" s="24" t="str">
         <x:f>D55&amp;"/"&amp;E55</x:f>
-        <x:v>1/1</x:v>
+        <x:v>3/7</x:v>
       </x:c>
       <x:c r="D55" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E55" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F55" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G55" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H55" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I55" s="18" t="str">
-        <x:v>Deathrattle: Summon Galactus (8/8)</x:v>
+        <x:v>Taunt. Passive: All other Taunt minions have +2/+2</x:v>
       </x:c>
       <x:c r="J55" s="18" t="str">
-        <x:v>The tide brings worlds.</x:v>
+        <x:v>The shield watches from orbit.</x:v>
       </x:c>
       <x:c r="K55" s="18" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L55" s="17" t="str">
-        <x:v>c032</x:v>
+        <x:v>c177</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
@@ -2651,38 +2651,38 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="14" t="str">
-        <x:v>Star Destroyer</x:v>
+        <x:v>Silver Surfer</x:v>
       </x:c>
       <x:c r="C56" s="23" t="str">
         <x:f>D56&amp;"/"&amp;E56</x:f>
-        <x:v>5/5</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D56" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E56" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F56" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G56" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H56" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I56" s="13" t="str">
-        <x:v>Battlecry: Summon two 1/1 TIE Fighters with Charge</x:v>
+        <x:v>Deathrattle: Summon Galactus (8/8)</x:v>
       </x:c>
       <x:c r="J56" s="13" t="str">
-        <x:v>-</x:v>
+        <x:v>The tide brings worlds.</x:v>
       </x:c>
       <x:c r="K56" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L56" s="12" t="str">
-        <x:v>c068</x:v>
+        <x:v>c032</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
@@ -2690,38 +2690,38 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="19" t="str">
-        <x:v>The 7 Heroic Spirits</x:v>
+        <x:v>Star Destroyer</x:v>
       </x:c>
       <x:c r="C57" s="24" t="str">
         <x:f>D57&amp;"/"&amp;E57</x:f>
-        <x:v>2/2</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D57" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E57" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F57" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G57" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H57" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I57" s="18" t="str">
-        <x:v>Battlecry: All your other minions gain a random Ascension Relic</x:v>
+        <x:v>Battlecry: Summon two 1/1 TIE Fighters with Charge</x:v>
       </x:c>
       <x:c r="J57" s="18" t="str">
-        <x:v>Legends reborn</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K57" s="18" t="str">
-        <x:v>Fate</x:v>
+        <x:v>Star Wars</x:v>
       </x:c>
       <x:c r="L57" s="17" t="str">
-        <x:v>c101</x:v>
+        <x:v>c068</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="44" customHeight="1">
@@ -2841,22 +2841,22 @@
         <x:v>c010</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="44" customHeight="1">
+    <x:row r="61" ht="42" customHeight="1">
       <x:c r="A61" s="22" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B61" s="19" t="str">
-        <x:v>Dominion Authority</x:v>
+        <x:v>Cthulhu</x:v>
       </x:c>
       <x:c r="C61" s="24" t="str">
         <x:f>D61&amp;"/"&amp;E61</x:f>
-        <x:v>4/5</x:v>
+        <x:v>6/6</x:v>
       </x:c>
       <x:c r="D61" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E61" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F61" s="24" t="str">
         <x:v>Rare</x:v>
@@ -2865,19 +2865,19 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H61" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I61" s="18" t="str">
-        <x:v>Passive: Friendly minions cannot be mind-controlled, returned to hand, or transformed by enemy effects</x:v>
+        <x:v>Chained. Passive: Immune to Tech minions</x:v>
       </x:c>
       <x:c r="J61" s="18" t="str">
-        <x:v>Loyalty</x:v>
+        <x:v>He dreams</x:v>
       </x:c>
       <x:c r="K61" s="18" t="str">
-        <x:v>Overlord</x:v>
+        <x:v>Myth</x:v>
       </x:c>
       <x:c r="L61" s="17" t="str">
-        <x:v>c086</x:v>
+        <x:v>c136</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="42" customHeight="1">
@@ -2919,82 +2919,82 @@
         <x:v>c097</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="44" customHeight="1">
+    <x:row r="63" ht="42" customHeight="1">
       <x:c r="A63" s="22" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B63" s="19" t="str">
-        <x:v>Floor Guardians</x:v>
+        <x:v>Founding Titan</x:v>
       </x:c>
       <x:c r="C63" s="24" t="str">
         <x:f>D63&amp;"/"&amp;E63</x:f>
-        <x:v>4/4</x:v>
+        <x:v>4/5</x:v>
       </x:c>
       <x:c r="D63" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E63" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F63" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G63" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H63" s="24" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I63" s="18" t="str">
-        <x:v>Battlecry: Choose 1 friendly minion board slot. Minions on that board slot gain +1/+1 at the start of your turn</x:v>
+        <x:v>Taunt. Passive: All friendly minions have Taunt</x:v>
       </x:c>
       <x:c r="J63" s="18" t="str">
-        <x:v>They do not guard the floors—they own them</x:v>
+        <x:v>The walls were never meant to protect</x:v>
       </x:c>
       <x:c r="K63" s="18" t="str">
-        <x:v>Overlord</x:v>
+        <x:v>Attack on Titan</x:v>
       </x:c>
       <x:c r="L63" s="17" t="str">
-        <x:v>c083</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="42" customHeight="1">
+        <x:v>c087</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="44" customHeight="1">
       <x:c r="A64" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>Founding Titan</x:v>
+        <x:v>Frieren</x:v>
       </x:c>
       <x:c r="C64" s="23" t="str">
         <x:f>D64&amp;"/"&amp;E64</x:f>
-        <x:v>4/5</x:v>
+        <x:v>2/5</x:v>
       </x:c>
       <x:c r="D64" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E64" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F64" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G64" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H64" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I64" s="13" t="str">
-        <x:v>Taunt. Passive: All friendly minions have Taunt</x:v>
+        <x:v>Passive: The first time you cast a relic each turn, discover another relic</x:v>
       </x:c>
       <x:c r="J64" s="13" t="str">
-        <x:v>The walls were never meant to protect</x:v>
+        <x:v>Every spell is worth remembering.</x:v>
       </x:c>
       <x:c r="K64" s="13" t="str">
-        <x:v>Attack on Titan</x:v>
+        <x:v>Frieren: Beyond Journey's End</x:v>
       </x:c>
       <x:c r="L64" s="12" t="str">
-        <x:v>c087</x:v>
+        <x:v>c184</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="44" customHeight="1">
@@ -3002,20 +3002,20 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B65" s="19" t="str">
-        <x:v>Frieren</x:v>
+        <x:v>Gandalf the White</x:v>
       </x:c>
       <x:c r="C65" s="24" t="str">
         <x:f>D65&amp;"/"&amp;E65</x:f>
-        <x:v>2/5</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D65" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E65" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F65" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G65" s="24" t="str">
         <x:v>Magic</x:v>
@@ -3024,16 +3024,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I65" s="18" t="str">
-        <x:v>Passive: The first time you cast a relic each turn, discover another relic</x:v>
+        <x:v>Divine Shield. Battlecry: Give all friendly Good minions Divine Shield</x:v>
       </x:c>
       <x:c r="J65" s="18" t="str">
-        <x:v>Every spell is worth remembering.</x:v>
+        <x:v>An incarnated angel</x:v>
       </x:c>
       <x:c r="K65" s="18" t="str">
-        <x:v>Frieren: Beyond Journey's End</x:v>
+        <x:v>Lord of the Rings</x:v>
       </x:c>
       <x:c r="L65" s="17" t="str">
-        <x:v>c184</x:v>
+        <x:v>c080</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="44" customHeight="1">
@@ -3041,38 +3041,38 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
-        <x:v>Gandalf the White</x:v>
+        <x:v>Homelander</x:v>
       </x:c>
       <x:c r="C66" s="23" t="str">
         <x:f>D66&amp;"/"&amp;E66</x:f>
-        <x:v>2/2</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D66" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E66" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F66" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G66" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H66" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I66" s="13" t="str">
-        <x:v>Divine Shield. Battlecry: Give all friendly Good minions Divine Shield</x:v>
+        <x:v>Passive: This minion is Invulnerable if it is your only minion on the board</x:v>
       </x:c>
       <x:c r="J66" s="13" t="str">
-        <x:v>An incarnated angel</x:v>
+        <x:v>Central casting</x:v>
       </x:c>
       <x:c r="K66" s="13" t="str">
-        <x:v>Lord of the Rings</x:v>
+        <x:v>The Boys</x:v>
       </x:c>
       <x:c r="L66" s="12" t="str">
-        <x:v>c080</x:v>
+        <x:v>c088</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="44" customHeight="1">
@@ -3080,77 +3080,77 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B67" s="19" t="str">
-        <x:v>Homelander</x:v>
+        <x:v>Kratos</x:v>
       </x:c>
       <x:c r="C67" s="24" t="str">
         <x:f>D67&amp;"/"&amp;E67</x:f>
-        <x:v>4/4</x:v>
+        <x:v>2/6</x:v>
       </x:c>
       <x:c r="D67" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E67" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F67" s="24" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G67" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H67" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I67" s="18" t="str">
-        <x:v>Passive: This minion is Invulnerable if it is your only minion on the board</x:v>
+        <x:v>Passive: Your opponent cannot play Ascension Relics or use Hero power</x:v>
       </x:c>
       <x:c r="J67" s="18" t="str">
-        <x:v>Central casting</x:v>
+        <x:v>He killed the gods of his world</x:v>
       </x:c>
       <x:c r="K67" s="18" t="str">
-        <x:v>The Boys</x:v>
+        <x:v>God of War Game</x:v>
       </x:c>
       <x:c r="L67" s="17" t="str">
-        <x:v>c088</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="44" customHeight="1">
+        <x:v>c089</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
       <x:c r="A68" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
-        <x:v>Kratos</x:v>
+        <x:v>Light Yagami</x:v>
       </x:c>
       <x:c r="C68" s="23" t="str">
         <x:f>D68&amp;"/"&amp;E68</x:f>
-        <x:v>2/6</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D68" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E68" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F68" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G68" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H68" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I68" s="13" t="str">
-        <x:v>Passive: Your opponent cannot play Ascension Relics or use Hero power</x:v>
+        <x:v>Battlecry: Destroy an enemy Nature minion</x:v>
       </x:c>
       <x:c r="J68" s="13" t="str">
-        <x:v>He killed the gods of his world</x:v>
+        <x:v>Ryuk, come help.</x:v>
       </x:c>
       <x:c r="K68" s="13" t="str">
-        <x:v>God of War Game</x:v>
+        <x:v>Death Note</x:v>
       </x:c>
       <x:c r="L68" s="12" t="str">
-        <x:v>c089</x:v>
+        <x:v>c021</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="42" customHeight="1">
@@ -3192,139 +3192,139 @@
         <x:v>c082</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="44" customHeight="1">
+    <x:row r="70" ht="42" customHeight="1">
       <x:c r="A70" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
-        <x:v>Meruem</x:v>
+        <x:v>Prince Lloyd</x:v>
       </x:c>
       <x:c r="C70" s="23" t="str">
         <x:f>D70&amp;"/"&amp;E70</x:f>
-        <x:v>4/5</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D70" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E70" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F70" s="23" t="str">
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G70" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H70" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I70" s="13" t="str">
-        <x:v>Passive: Whenever Meruem kills a minion, gain +1/+1 and gain its effects</x:v>
+        <x:v>Divine Shield. Passive: Other friendly minions take 1 less damage</x:v>
       </x:c>
       <x:c r="J70" s="13" t="str">
-        <x:v>Loyalty</x:v>
+        <x:v>Magic is all he ever wanted to perfect.</x:v>
       </x:c>
       <x:c r="K70" s="13" t="str">
-        <x:v>HxH</x:v>
+        <x:v>7th Prince</x:v>
       </x:c>
       <x:c r="L70" s="12" t="str">
-        <x:v>c084</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="42" customHeight="1">
+        <x:v>c180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="44" customHeight="1">
       <x:c r="A71" s="22" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B71" s="19" t="str">
-        <x:v>Prince Lloyd</x:v>
+        <x:v>Shigaraki</x:v>
       </x:c>
       <x:c r="C71" s="24" t="str">
         <x:f>D71&amp;"/"&amp;E71</x:f>
-        <x:v>2/2</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D71" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E71" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F71" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G71" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H71" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I71" s="18" t="str">
-        <x:v>Divine Shield. Passive: Other friendly minions take 1 less damage</x:v>
+        <x:v>Passive: Whenever Shigaraki damages a minion, mark it. At the start of your next turn, it dies</x:v>
       </x:c>
       <x:c r="J71" s="18" t="str">
-        <x:v>Magic is all he ever wanted to perfect.</x:v>
+        <x:v>Revenge</x:v>
       </x:c>
       <x:c r="K71" s="18" t="str">
-        <x:v>7th Prince</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L71" s="17" t="str">
-        <x:v>c180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="44" customHeight="1">
+        <x:v>c090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
       <x:c r="A72" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
-        <x:v>Ragnaros</x:v>
+        <x:v>Sonic</x:v>
       </x:c>
       <x:c r="C72" s="23" t="str">
         <x:f>D72&amp;"/"&amp;E72</x:f>
-        <x:v>6/6</x:v>
+        <x:v>6/3</x:v>
       </x:c>
       <x:c r="D72" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E72" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F72" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G72" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H72" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I72" s="13" t="str">
-        <x:v>Cannot attack. Ongoing: Deal 3 damage to a random enemy minion or the enemy core</x:v>
+        <x:v>Charge</x:v>
       </x:c>
       <x:c r="J72" s="13" t="str">
-        <x:v>Summoned. Once again.</x:v>
+        <x:v>SS</x:v>
       </x:c>
       <x:c r="K72" s="13" t="str">
-        <x:v>Hearthstone</x:v>
+        <x:v>Sonic The Hedgehog</x:v>
       </x:c>
       <x:c r="L72" s="12" t="str">
-        <x:v>c031</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="44" customHeight="1">
+        <x:v>c085</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="42" customHeight="1">
       <x:c r="A73" s="22" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B73" s="19" t="str">
-        <x:v>Shigaraki</x:v>
+        <x:v>Ten Commandments</x:v>
       </x:c>
       <x:c r="C73" s="24" t="str">
         <x:f>D73&amp;"/"&amp;E73</x:f>
-        <x:v>4/4</x:v>
+        <x:v>3/5</x:v>
       </x:c>
       <x:c r="D73" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E73" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F73" s="24" t="str">
         <x:v>Rare</x:v>
@@ -3336,31 +3336,31 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I73" s="18" t="str">
-        <x:v>Passive: Whenever Shigaraki damages a minion, mark it. At the start of your next turn, it dies</x:v>
+        <x:v>Passive: The first enemy minion to attack each turn is Chained</x:v>
       </x:c>
       <x:c r="J73" s="18" t="str">
-        <x:v>Revenge</x:v>
+        <x:v>Their reputation preceded them by centuries</x:v>
       </x:c>
       <x:c r="K73" s="18" t="str">
-        <x:v>MHA</x:v>
+        <x:v>Seven Deadly Sins</x:v>
       </x:c>
       <x:c r="L73" s="17" t="str">
-        <x:v>c090</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="42" customHeight="1">
+        <x:v>c091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="44" customHeight="1">
       <x:c r="A74" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
-        <x:v>Sonic</x:v>
+        <x:v>The Mask</x:v>
       </x:c>
       <x:c r="C74" s="23" t="str">
         <x:f>D74&amp;"/"&amp;E74</x:f>
-        <x:v>6/3</x:v>
+        <x:v>4/3</x:v>
       </x:c>
       <x:c r="D74" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E74" s="21" t="n">
         <x:v>3</x:v>
@@ -3369,22 +3369,22 @@
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G74" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H74" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I74" s="13" t="str">
-        <x:v>Charge</x:v>
+        <x:v>Battlecry: Transform your minions into random ones that cost 1 more mana</x:v>
       </x:c>
       <x:c r="J74" s="13" t="str">
-        <x:v>SS</x:v>
+        <x:v>True nature, revealed</x:v>
       </x:c>
       <x:c r="K74" s="13" t="str">
-        <x:v>Sonic The Hedgehog</x:v>
+        <x:v>The Mask</x:v>
       </x:c>
       <x:c r="L74" s="12" t="str">
-        <x:v>c085</x:v>
+        <x:v>c116</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="42" customHeight="1">
@@ -3392,20 +3392,20 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B75" s="19" t="str">
-        <x:v>Ten Commandments</x:v>
+        <x:v>Thirteen Lords of Chaos</x:v>
       </x:c>
       <x:c r="C75" s="24" t="str">
         <x:f>D75&amp;"/"&amp;E75</x:f>
-        <x:v>3/5</x:v>
+        <x:v>4/2</x:v>
       </x:c>
       <x:c r="D75" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E75" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F75" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G75" s="24" t="str">
         <x:v>Magic</x:v>
@@ -3414,31 +3414,31 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I75" s="18" t="str">
-        <x:v>Passive: The first enemy minion to attack each turn is Chained</x:v>
+        <x:v>Deathrattle: Summon Drakath (5/3)</x:v>
       </x:c>
       <x:c r="J75" s="18" t="str">
-        <x:v>Their reputation preceded them by centuries</x:v>
+        <x:v>Reality picks a side.</x:v>
       </x:c>
       <x:c r="K75" s="18" t="str">
-        <x:v>Seven Deadly Sins</x:v>
+        <x:v>AQW</x:v>
       </x:c>
       <x:c r="L75" s="17" t="str">
-        <x:v>c091</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="44" customHeight="1">
+        <x:v>c011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="42" customHeight="1">
       <x:c r="A76" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
-        <x:v>The Mask</x:v>
+        <x:v>Toji</x:v>
       </x:c>
       <x:c r="C76" s="23" t="str">
         <x:f>D76&amp;"/"&amp;E76</x:f>
-        <x:v>4/3</x:v>
+        <x:v>5/3</x:v>
       </x:c>
       <x:c r="D76" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E76" s="21" t="n">
         <x:v>3</x:v>
@@ -3447,22 +3447,22 @@
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G76" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H76" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I76" s="13" t="str">
-        <x:v>Battlecry: Transform your minions into random ones that cost 1 more mana</x:v>
+        <x:v>Passive: Immune to Magic minions</x:v>
       </x:c>
       <x:c r="J76" s="13" t="str">
-        <x:v>True nature, revealed</x:v>
+        <x:v>No magic. No mercy.</x:v>
       </x:c>
       <x:c r="K76" s="13" t="str">
-        <x:v>The Mask</x:v>
+        <x:v>Jujutsu Kaisen</x:v>
       </x:c>
       <x:c r="L76" s="12" t="str">
-        <x:v>c116</x:v>
+        <x:v>c040</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="42" customHeight="1">
@@ -3470,173 +3470,173 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B77" s="19" t="str">
-        <x:v>Thirteen Lords of Chaos</x:v>
+        <x:v>UFO</x:v>
       </x:c>
       <x:c r="C77" s="24" t="str">
         <x:f>D77&amp;"/"&amp;E77</x:f>
-        <x:v>4/2</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D77" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E77" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F77" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G77" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H77" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I77" s="18" t="str">
-        <x:v>Deathrattle: Summon Drakath (5/3)</x:v>
+        <x:v>Divine Shield</x:v>
       </x:c>
       <x:c r="J77" s="18" t="str">
-        <x:v>Reality picks a side.</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K77" s="18" t="str">
-        <x:v>AQW</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L77" s="17" t="str">
-        <x:v>c011</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="42" customHeight="1">
+        <x:v>c092</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="44" customHeight="1">
       <x:c r="A78" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>Time Bomb</x:v>
+        <x:v>Buddha</x:v>
       </x:c>
       <x:c r="C78" s="23" t="str">
         <x:f>D78&amp;"/"&amp;E78</x:f>
-        <x:v>0/9</x:v>
+        <x:v>3/4</x:v>
       </x:c>
       <x:c r="D78" s="21" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E78" s="21" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F78" s="23" t="str">
         <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G78" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H78" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I78" s="13" t="str">
-        <x:v>Ongoing: Destroy ALL minions</x:v>
+        <x:v>Battlecry: All minions become Good type. Clear Chained, Frozen, Silenced and Marked from every minion on the board</x:v>
       </x:c>
       <x:c r="J78" s="13" t="str">
-        <x:v>Timer is T-1.</x:v>
+        <x:v>Peace.</x:v>
       </x:c>
       <x:c r="K78" s="13" t="str">
-        <x:v>Loki</x:v>
+        <x:v>Record of Ragnarok</x:v>
       </x:c>
       <x:c r="L78" s="12" t="str">
-        <x:v>c009</x:v>
+        <x:v>c038</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="42" customHeight="1">
       <x:c r="A79" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B79" s="19" t="str">
-        <x:v>Toji</x:v>
+        <x:v>Carrier Strike Group</x:v>
       </x:c>
       <x:c r="C79" s="24" t="str">
         <x:f>D79&amp;"/"&amp;E79</x:f>
-        <x:v>5/3</x:v>
+        <x:v>1/5</x:v>
       </x:c>
       <x:c r="D79" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E79" s="22" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E79" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="F79" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G79" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H79" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I79" s="18" t="str">
-        <x:v>Passive: Immune to Magic minions</x:v>
+        <x:v>Passive: Enemy Tech minions cannot attack</x:v>
       </x:c>
       <x:c r="J79" s="18" t="str">
-        <x:v>No magic. No mercy.</x:v>
+        <x:v>The horizon belongs to the fleet.</x:v>
       </x:c>
       <x:c r="K79" s="18" t="str">
-        <x:v>Jujutsu Kaisen</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L79" s="17" t="str">
-        <x:v>c040</x:v>
+        <x:v>c187</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="42" customHeight="1">
       <x:c r="A80" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>UFO</x:v>
+        <x:v>Chaos</x:v>
       </x:c>
       <x:c r="C80" s="23" t="str">
         <x:f>D80&amp;"/"&amp;E80</x:f>
-        <x:v>3/3</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D80" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E80" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F80" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G80" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H80" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I80" s="13" t="str">
-        <x:v>Divine Shield</x:v>
+        <x:v>Battlecry: Summon a random minion from your deck</x:v>
       </x:c>
       <x:c r="J80" s="13" t="str">
-        <x:v>-</x:v>
+        <x:v>He gives gifts. He never mentions the cost</x:v>
       </x:c>
       <x:c r="K80" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Hades</x:v>
       </x:c>
       <x:c r="L80" s="12" t="str">
-        <x:v>c092</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="44" customHeight="1">
+        <x:v>c061</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="42" customHeight="1">
       <x:c r="A81" s="22" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B81" s="19" t="str">
-        <x:v>Big Mom</x:v>
+        <x:v>Darth Vader</x:v>
       </x:c>
       <x:c r="C81" s="24" t="str">
         <x:f>D81&amp;"/"&amp;E81</x:f>
-        <x:v>3/5</x:v>
+        <x:v>3/2</x:v>
       </x:c>
       <x:c r="D81" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E81" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F81" s="24" t="str">
         <x:v>Epic</x:v>
@@ -3648,34 +3648,34 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I81" s="18" t="str">
-        <x:v>Battlecry: Destroy a friendly minion. Gain its ATK and HP, in addition to your own</x:v>
+        <x:v>Battlecry: Choose an enemy minion. Set its ATK to 1 and Chain it</x:v>
       </x:c>
       <x:c r="J81" s="18" t="str">
-        <x:v>Greed</x:v>
+        <x:v>Reborn.</x:v>
       </x:c>
       <x:c r="K81" s="18" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>Star Wars</x:v>
       </x:c>
       <x:c r="L81" s="17" t="str">
-        <x:v>c098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="44" customHeight="1">
+        <x:v>c029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="42" customHeight="1">
       <x:c r="A82" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>Buddha</x:v>
+        <x:v>Dio Brando</x:v>
       </x:c>
       <x:c r="C82" s="23" t="str">
         <x:f>D82&amp;"/"&amp;E82</x:f>
-        <x:v>3/4</x:v>
+        <x:v>3/2</x:v>
       </x:c>
       <x:c r="D82" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E82" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F82" s="23" t="str">
         <x:v>Legendary</x:v>
@@ -3684,19 +3684,19 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H82" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I82" s="13" t="str">
-        <x:v>Battlecry: All minions become Good type. Clear Chained, Frozen, Silenced and Marked from every minion on the board</x:v>
+        <x:v>Battlecry: Freeze all enemy minions</x:v>
       </x:c>
       <x:c r="J82" s="13" t="str">
-        <x:v>Peace.</x:v>
+        <x:v>THE WORLD</x:v>
       </x:c>
       <x:c r="K82" s="13" t="str">
-        <x:v>Record of Ragnarok</x:v>
+        <x:v>JoJo</x:v>
       </x:c>
       <x:c r="L82" s="12" t="str">
-        <x:v>c038</x:v>
+        <x:v>c096</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="42" customHeight="1">
@@ -3704,53 +3704,53 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B83" s="19" t="str">
-        <x:v>Darth Vader</x:v>
+        <x:v>Dragon</x:v>
       </x:c>
       <x:c r="C83" s="24" t="str">
         <x:f>D83&amp;"/"&amp;E83</x:f>
-        <x:v>3/2</x:v>
+        <x:v>3/5</x:v>
       </x:c>
       <x:c r="D83" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E83" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F83" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G83" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H83" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I83" s="18" t="str">
-        <x:v>Battlecry: Choose an enemy minion. Set its ATK to 1 and Chain it</x:v>
+        <x:v>Taunt</x:v>
       </x:c>
       <x:c r="J83" s="18" t="str">
-        <x:v>Reborn.</x:v>
+        <x:v>ROAR</x:v>
       </x:c>
       <x:c r="K83" s="18" t="str">
-        <x:v>Star Wars</x:v>
+        <x:v>Myth</x:v>
       </x:c>
       <x:c r="L83" s="17" t="str">
-        <x:v>c029</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="42" customHeight="1">
+        <x:v>c102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="44" customHeight="1">
       <x:c r="A84" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
-        <x:v>Deep Sea King</x:v>
+        <x:v>Dumbledore</x:v>
       </x:c>
       <x:c r="C84" s="23" t="str">
         <x:f>D84&amp;"/"&amp;E84</x:f>
-        <x:v>4/4</x:v>
+        <x:v>2/4</x:v>
       </x:c>
       <x:c r="D84" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E84" s="21" t="n">
         <x:v>4</x:v>
@@ -3759,22 +3759,22 @@
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G84" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H84" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I84" s="13" t="str">
-        <x:v>Passive: Costs 3 less while any minion is Frozen or Chained</x:v>
+        <x:v>Passive: Friendly minions cannot be Silenced, Frozen, or Chained. Undo any such curses</x:v>
       </x:c>
       <x:c r="J84" s="13" t="str">
-        <x:v>This is why you stay out of the ocean.</x:v>
+        <x:v>He always asks calmly.</x:v>
       </x:c>
       <x:c r="K84" s="13" t="str">
-        <x:v>OPM</x:v>
+        <x:v>Harry Potter</x:v>
       </x:c>
       <x:c r="L84" s="12" t="str">
-        <x:v>c039</x:v>
+        <x:v>c030</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="42" customHeight="1">
@@ -3782,20 +3782,20 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B85" s="19" t="str">
-        <x:v>Dio Brando</x:v>
+        <x:v>Fire Lord Ozai</x:v>
       </x:c>
       <x:c r="C85" s="24" t="str">
         <x:f>D85&amp;"/"&amp;E85</x:f>
-        <x:v>3/2</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D85" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E85" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F85" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G85" s="24" t="str">
         <x:v>Magic</x:v>
@@ -3804,55 +3804,55 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I85" s="18" t="str">
-        <x:v>Battlecry: Freeze all enemy minions</x:v>
+        <x:v>Battlecry: Deal 2 damage to all other minions</x:v>
       </x:c>
       <x:c r="J85" s="18" t="str">
-        <x:v>THE WORLD</x:v>
+        <x:v>Entitlement</x:v>
       </x:c>
       <x:c r="K85" s="18" t="str">
-        <x:v>JoJo</x:v>
+        <x:v>Avatar</x:v>
       </x:c>
       <x:c r="L85" s="17" t="str">
-        <x:v>c096</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="42" customHeight="1">
+        <x:v>c099</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="44" customHeight="1">
       <x:c r="A86" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
-        <x:v>Dragon</x:v>
+        <x:v>GLaDOS</x:v>
       </x:c>
       <x:c r="C86" s="23" t="str">
         <x:f>D86&amp;"/"&amp;E86</x:f>
-        <x:v>3/5</x:v>
+        <x:v>2/3</x:v>
       </x:c>
       <x:c r="D86" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E86" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F86" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G86" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H86" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I86" s="13" t="str">
-        <x:v>Taunt</x:v>
+        <x:v>Cannot attack. Passive: Adjacent friendly Tech minions have Taunt and +2/+2</x:v>
       </x:c>
       <x:c r="J86" s="13" t="str">
-        <x:v>ROAR</x:v>
+        <x:v>The test continues</x:v>
       </x:c>
       <x:c r="K86" s="13" t="str">
-        <x:v>Myth</x:v>
+        <x:v>Portal</x:v>
       </x:c>
       <x:c r="L86" s="12" t="str">
-        <x:v>c102</x:v>
+        <x:v>c104</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="44" customHeight="1">
@@ -3860,20 +3860,20 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B87" s="19" t="str">
-        <x:v>Dumbledore</x:v>
+        <x:v>Grand Master Oogway</x:v>
       </x:c>
       <x:c r="C87" s="24" t="str">
         <x:f>D87&amp;"/"&amp;E87</x:f>
-        <x:v>2/4</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D87" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E87" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F87" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G87" s="24" t="str">
         <x:v>Magic</x:v>
@@ -3882,63 +3882,63 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I87" s="18" t="str">
-        <x:v>Passive: Friendly minions cannot be Silenced, Frozen, or Chained. Undo any such curses</x:v>
+        <x:v>Divine Shield. Passive: Once per turn, when another friendly minion would die, return it to your hand instead and Chain Oogway</x:v>
       </x:c>
       <x:c r="J87" s="18" t="str">
-        <x:v>He always asks calmly.</x:v>
+        <x:v>Patience</x:v>
       </x:c>
       <x:c r="K87" s="18" t="str">
-        <x:v>Harry Potter</x:v>
+        <x:v>Kung-Fu Panda</x:v>
       </x:c>
       <x:c r="L87" s="17" t="str">
-        <x:v>c030</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="42" customHeight="1">
+        <x:v>c094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="44" customHeight="1">
       <x:c r="A88" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
-        <x:v>Eye of Sauron</x:v>
+        <x:v>Kojiro Sasaki</x:v>
       </x:c>
       <x:c r="C88" s="23" t="str">
         <x:f>D88&amp;"/"&amp;E88</x:f>
-        <x:v>1/5</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D88" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E88" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F88" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G88" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H88" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I88" s="13" t="str">
-        <x:v>Passive: Enemy cards cost 1 more</x:v>
+        <x:v>Passive: All friendly minions have +33% chance to evade an attack</x:v>
       </x:c>
       <x:c r="J88" s="13" t="str">
-        <x:v>Try and hide.</x:v>
+        <x:v>Spending infinity in the Astral made him on par with the Gods</x:v>
       </x:c>
       <x:c r="K88" s="13" t="str">
-        <x:v>Lord of the Rings</x:v>
+        <x:v>RoR</x:v>
       </x:c>
       <x:c r="L88" s="12" t="str">
-        <x:v>c037</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="42" customHeight="1">
+        <x:v>c095</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="44" customHeight="1">
       <x:c r="A89" s="22" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B89" s="19" t="str">
-        <x:v>Fire Lord Ozai</x:v>
+        <x:v>Kuma</x:v>
       </x:c>
       <x:c r="C89" s="24" t="str">
         <x:f>D89&amp;"/"&amp;E89</x:f>
@@ -3954,61 +3954,61 @@
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G89" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H89" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I89" s="18" t="str">
-        <x:v>Battlecry: Deal 2 damage to all other minions</x:v>
+        <x:v>Battlecry: Return a friendly minion to your hand. It costs 5 less the next time it is played this game</x:v>
       </x:c>
       <x:c r="J89" s="18" t="str">
-        <x:v>Entitlement</x:v>
+        <x:v>Weapon</x:v>
       </x:c>
       <x:c r="K89" s="18" t="str">
-        <x:v>Avatar</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L89" s="17" t="str">
-        <x:v>c099</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="42" customHeight="1">
+        <x:v>c133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="44" customHeight="1">
       <x:c r="A90" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B90" s="14" t="str">
-        <x:v>Fort</x:v>
+        <x:v>One-Eyed Owl</x:v>
       </x:c>
       <x:c r="C90" s="23" t="str">
         <x:f>D90&amp;"/"&amp;E90</x:f>
-        <x:v>4/5</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D90" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E90" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F90" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G90" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H90" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I90" s="13" t="str">
-        <x:v>Taunt. Cannot attack</x:v>
+        <x:v>Passive: Whenever a minion becomes Chained, Frozen or Silenced, gain +1/+1</x:v>
       </x:c>
       <x:c r="J90" s="13" t="str">
-        <x:v>-</x:v>
+        <x:v>All seeing eye</x:v>
       </x:c>
       <x:c r="K90" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Tokyo Ghoul</x:v>
       </x:c>
       <x:c r="L90" s="12" t="str">
-        <x:v>c103</x:v>
+        <x:v>c115</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="44" customHeight="1">
@@ -4016,155 +4016,155 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B91" s="19" t="str">
-        <x:v>GLaDOS</x:v>
+        <x:v>Pandora's Actor</x:v>
       </x:c>
       <x:c r="C91" s="24" t="str">
         <x:f>D91&amp;"/"&amp;E91</x:f>
-        <x:v>2/3</x:v>
+        <x:v>5/5</x:v>
       </x:c>
       <x:c r="D91" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E91" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F91" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G91" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H91" s="24" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I91" s="18" t="str">
-        <x:v>Cannot attack. Passive: Adjacent friendly Tech minions have Taunt and +2/+2</x:v>
+        <x:v>Battlecry: Choose another minion. Become it. HP and ATK are not copied</x:v>
       </x:c>
       <x:c r="J91" s="18" t="str">
-        <x:v>The test continues</x:v>
+        <x:v>Every role is useful.</x:v>
       </x:c>
       <x:c r="K91" s="18" t="str">
-        <x:v>Portal</x:v>
+        <x:v>Overlord</x:v>
       </x:c>
       <x:c r="L91" s="17" t="str">
-        <x:v>c104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="44" customHeight="1">
+        <x:v>c007</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="42" customHeight="1">
       <x:c r="A92" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>Grand Master Oogway</x:v>
+        <x:v>Rennala Queen of the Full Moon</x:v>
       </x:c>
       <x:c r="C92" s="23" t="str">
         <x:f>D92&amp;"/"&amp;E92</x:f>
-        <x:v>2/2</x:v>
+        <x:v>2/3</x:v>
       </x:c>
       <x:c r="D92" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E92" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F92" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G92" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H92" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I92" s="13" t="str">
-        <x:v>Divine Shield. Passive: Once per turn, when another friendly minion would die, return it to your hand instead and Chain Oogway</x:v>
+        <x:v>Battlecry: Rebirth a random friendly minion that died this game</x:v>
       </x:c>
       <x:c r="J92" s="13" t="str">
-        <x:v>Patience</x:v>
+        <x:v>The Moon</x:v>
       </x:c>
       <x:c r="K92" s="13" t="str">
-        <x:v>Kung-Fu Panda</x:v>
+        <x:v>Elden Ring</x:v>
       </x:c>
       <x:c r="L92" s="12" t="str">
-        <x:v>c094</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="44" customHeight="1">
+        <x:v>c100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="42" customHeight="1">
       <x:c r="A93" s="22" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B93" s="19" t="str">
-        <x:v>Kojiro Sasaki</x:v>
+        <x:v>T-1000</x:v>
       </x:c>
       <x:c r="C93" s="24" t="str">
         <x:f>D93&amp;"/"&amp;E93</x:f>
-        <x:v>2/2</x:v>
+        <x:v>3/5</x:v>
       </x:c>
       <x:c r="D93" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E93" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F93" s="24" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G93" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H93" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I93" s="18" t="str">
-        <x:v>Passive: All friendly minions have +33% chance to evade an attack</x:v>
+        <x:v>Ongoing: Fully heal yourself</x:v>
       </x:c>
       <x:c r="J93" s="18" t="str">
-        <x:v>Spending infinity in the Astral made him on par with the Gods</x:v>
+        <x:v>It remembers its shape.</x:v>
       </x:c>
       <x:c r="K93" s="18" t="str">
-        <x:v>RoR</x:v>
+        <x:v>Terminator</x:v>
       </x:c>
       <x:c r="L93" s="17" t="str">
-        <x:v>c095</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="44" customHeight="1">
+        <x:v>c008</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="42" customHeight="1">
       <x:c r="A94" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B94" s="14" t="str">
-        <x:v>One-Eyed Owl</x:v>
+        <x:v>The Driller</x:v>
       </x:c>
       <x:c r="C94" s="23" t="str">
         <x:f>D94&amp;"/"&amp;E94</x:f>
-        <x:v>4/4</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D94" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E94" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F94" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G94" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H94" s="23" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I94" s="13" t="str">
-        <x:v>Passive: Whenever a minion becomes Chained, Frozen or Silenced, gain +1/+1</x:v>
+        <x:v>Battlecry: Consume an enemy Tech minion with 4 HP or lower</x:v>
       </x:c>
       <x:c r="J94" s="13" t="str">
-        <x:v>All seeing eye</x:v>
+        <x:v>Latest design</x:v>
       </x:c>
       <x:c r="K94" s="13" t="str">
-        <x:v>Tokyo Ghoul</x:v>
+        <x:v>Transformers</x:v>
       </x:c>
       <x:c r="L94" s="12" t="str">
-        <x:v>c115</x:v>
+        <x:v>c105</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="42" customHeight="1">
@@ -4172,59 +4172,59 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B95" s="19" t="str">
-        <x:v>Rennala Queen of the Full Moon</x:v>
+        <x:v>Time Bomb</x:v>
       </x:c>
       <x:c r="C95" s="24" t="str">
         <x:f>D95&amp;"/"&amp;E95</x:f>
-        <x:v>2/3</x:v>
+        <x:v>0/9</x:v>
       </x:c>
       <x:c r="D95" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E95" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F95" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G95" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H95" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I95" s="18" t="str">
-        <x:v>Battlecry: Rebirth a random friendly minion that died this game</x:v>
+        <x:v>Ongoing: Destroy ALL minions</x:v>
       </x:c>
       <x:c r="J95" s="18" t="str">
-        <x:v>The Moon</x:v>
+        <x:v>Timer is T-1.</x:v>
       </x:c>
       <x:c r="K95" s="18" t="str">
-        <x:v>Elden Ring</x:v>
+        <x:v>Loki</x:v>
       </x:c>
       <x:c r="L95" s="17" t="str">
-        <x:v>c100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="42" customHeight="1">
+        <x:v>c009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="44" customHeight="1">
       <x:c r="A96" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B96" s="14" t="str">
-        <x:v>T-1000</x:v>
+        <x:v>Transformers</x:v>
       </x:c>
       <x:c r="C96" s="23" t="str">
         <x:f>D96&amp;"/"&amp;E96</x:f>
-        <x:v>3/5</x:v>
+        <x:v>2/5</x:v>
       </x:c>
       <x:c r="D96" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E96" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F96" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G96" s="23" t="str">
         <x:v>Tech</x:v>
@@ -4233,16 +4233,16 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I96" s="13" t="str">
-        <x:v>Ongoing: Fully heal yourself</x:v>
+        <x:v>Battlecry: Consume all friendly Tech minions and gain their stats and effects</x:v>
       </x:c>
       <x:c r="J96" s="13" t="str">
-        <x:v>It remembers its shape.</x:v>
+        <x:v>Cybertronian</x:v>
       </x:c>
       <x:c r="K96" s="13" t="str">
-        <x:v>Terminator</x:v>
+        <x:v>Transformers</x:v>
       </x:c>
       <x:c r="L96" s="12" t="str">
-        <x:v>c008</x:v>
+        <x:v>c106</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="42" customHeight="1">
@@ -4250,53 +4250,53 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B97" s="19" t="str">
-        <x:v>The Driller</x:v>
+        <x:v>Zoro</x:v>
       </x:c>
       <x:c r="C97" s="24" t="str">
         <x:f>D97&amp;"/"&amp;E97</x:f>
-        <x:v>1/1</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D97" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E97" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F97" s="24" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G97" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H97" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I97" s="18" t="str">
-        <x:v>Battlecry: Consume an enemy Tech minion with 4 HP or lower</x:v>
+        <x:v>Passive: Gain +1/+1 after killing a minion</x:v>
       </x:c>
       <x:c r="J97" s="18" t="str">
-        <x:v>Latest design</x:v>
+        <x:v>Lost again. Still won.</x:v>
       </x:c>
       <x:c r="K97" s="18" t="str">
-        <x:v>Transformers</x:v>
+        <x:v>One Piece</x:v>
       </x:c>
       <x:c r="L97" s="17" t="str">
-        <x:v>c105</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="44" customHeight="1">
+        <x:v>c142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="42" customHeight="1">
       <x:c r="A98" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B98" s="14" t="str">
-        <x:v>Transformers</x:v>
+        <x:v>Albion</x:v>
       </x:c>
       <x:c r="C98" s="23" t="str">
         <x:f>D98&amp;"/"&amp;E98</x:f>
-        <x:v>2/5</x:v>
+        <x:v>6/5</x:v>
       </x:c>
       <x:c r="D98" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E98" s="21" t="n">
         <x:v>5</x:v>
@@ -4305,61 +4305,61 @@
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G98" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H98" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I98" s="13" t="str">
-        <x:v>Battlecry: Consume all friendly Tech minions and gain their stats and effects</x:v>
+        <x:v>Chained</x:v>
       </x:c>
       <x:c r="J98" s="13" t="str">
-        <x:v>Cybertronian</x:v>
+        <x:v>Mountain-tall</x:v>
       </x:c>
       <x:c r="K98" s="13" t="str">
-        <x:v>Transformers</x:v>
+        <x:v>Seven Deadly Sins</x:v>
       </x:c>
       <x:c r="L98" s="12" t="str">
-        <x:v>c106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="42" customHeight="1">
+        <x:v>c117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="44" customHeight="1">
       <x:c r="A99" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B99" s="19" t="str">
-        <x:v>Zoro</x:v>
+        <x:v>Angstrom Levy</x:v>
       </x:c>
       <x:c r="C99" s="24" t="str">
         <x:f>D99&amp;"/"&amp;E99</x:f>
-        <x:v>4/4</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D99" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E99" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F99" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G99" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H99" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I99" s="18" t="str">
-        <x:v>Passive: Gain +1/+1 after killing a minion</x:v>
+        <x:v>Battlecry: Choose another minion. Put it on the bottom of the deck and summon a random minion of the same cost into its slot</x:v>
       </x:c>
       <x:c r="J99" s="18" t="str">
-        <x:v>Lost again. Still won.</x:v>
+        <x:v>Universe</x:v>
       </x:c>
       <x:c r="K99" s="18" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>Invincible</x:v>
       </x:c>
       <x:c r="L99" s="17" t="str">
-        <x:v>c142</x:v>
+        <x:v>c163</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="42" customHeight="1">
@@ -4367,38 +4367,38 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B100" s="14" t="str">
-        <x:v>Albion</x:v>
+        <x:v>Battleship</x:v>
       </x:c>
       <x:c r="C100" s="23" t="str">
         <x:f>D100&amp;"/"&amp;E100</x:f>
-        <x:v>6/5</x:v>
+        <x:v>2/3</x:v>
       </x:c>
       <x:c r="D100" s="21" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E100" s="21" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F100" s="23" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G100" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H100" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I100" s="13" t="str">
-        <x:v>Chained</x:v>
+        <x:v>Passive: All friendly Tech minions have +2/+1</x:v>
       </x:c>
       <x:c r="J100" s="13" t="str">
-        <x:v>Mountain-tall</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K100" s="13" t="str">
-        <x:v>Seven Deadly Sins</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L100" s="12" t="str">
-        <x:v>c117</x:v>
+        <x:v>c118</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="42" customHeight="1">
@@ -4406,77 +4406,77 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B101" s="19" t="str">
-        <x:v>Battleship</x:v>
+        <x:v>Carnage Kabuto</x:v>
       </x:c>
       <x:c r="C101" s="24" t="str">
         <x:f>D101&amp;"/"&amp;E101</x:f>
-        <x:v>2/3</x:v>
+        <x:v>3/2</x:v>
       </x:c>
       <x:c r="D101" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E101" s="22" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="E101" s="22" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="F101" s="24" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G101" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H101" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I101" s="18" t="str">
-        <x:v>Passive: All friendly Tech minions have +2/+1</x:v>
+        <x:v>Ongoing: Gain +3 ATK</x:v>
       </x:c>
       <x:c r="J101" s="18" t="str">
-        <x:v>-</x:v>
+        <x:v>Maximum evolution</x:v>
       </x:c>
       <x:c r="K101" s="18" t="str">
-        <x:v>Basic</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L101" s="17" t="str">
-        <x:v>c118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="42" customHeight="1">
+        <x:v>c119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="44" customHeight="1">
       <x:c r="A102" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B102" s="14" t="str">
-        <x:v>Carnage Kabuto</x:v>
+        <x:v>Chrollo</x:v>
       </x:c>
       <x:c r="C102" s="23" t="str">
         <x:f>D102&amp;"/"&amp;E102</x:f>
-        <x:v>3/2</x:v>
+        <x:v>3/5</x:v>
       </x:c>
       <x:c r="D102" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E102" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F102" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G102" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H102" s="23" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I102" s="13" t="str">
-        <x:v>Ongoing: Gain +3 ATK</x:v>
+        <x:v>Battlecry: Copy a passive from a minion. That minion loses the passive as long as Chrollo is alive</x:v>
       </x:c>
       <x:c r="J102" s="13" t="str">
-        <x:v>Maximum evolution</x:v>
+        <x:v>A poisonous spider</x:v>
       </x:c>
       <x:c r="K102" s="13" t="str">
-        <x:v>OPM</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L102" s="12" t="str">
-        <x:v>c119</x:v>
+        <x:v>c107</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="44" customHeight="1">
@@ -4484,38 +4484,38 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B103" s="19" t="str">
-        <x:v>Chrollo</x:v>
+        <x:v>Doctor Octopus</x:v>
       </x:c>
       <x:c r="C103" s="24" t="str">
         <x:f>D103&amp;"/"&amp;E103</x:f>
-        <x:v>3/5</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D103" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E103" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F103" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G103" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H103" s="24" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I103" s="18" t="str">
-        <x:v>Battlecry: Copy a passive from a minion. That minion loses the passive as long as Chrollo is alive</x:v>
+        <x:v>Battlecry: Destroy an enemy Ascension Relic (equipped by an enemy minion) of your choice</x:v>
       </x:c>
       <x:c r="J103" s="18" t="str">
-        <x:v>A poisonous spider</x:v>
+        <x:v>The power of the Sun, in the palm of my hands</x:v>
       </x:c>
       <x:c r="K103" s="18" t="str">
-        <x:v>HxH</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L103" s="17" t="str">
-        <x:v>c107</x:v>
+        <x:v>c111</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="44" customHeight="1">
@@ -4523,38 +4523,38 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B104" s="14" t="str">
-        <x:v>Doctor Octopus</x:v>
+        <x:v>Dominion Authority</x:v>
       </x:c>
       <x:c r="C104" s="23" t="str">
         <x:f>D104&amp;"/"&amp;E104</x:f>
-        <x:v>3/3</x:v>
+        <x:v>1/4</x:v>
       </x:c>
       <x:c r="D104" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E104" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F104" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G104" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H104" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I104" s="13" t="str">
-        <x:v>Battlecry: Destroy an enemy Ascension Relic (equipped by an enemy minion) of your choice</x:v>
+        <x:v>Passive: Friendly minions cannot be mind-controlled, returned to hand, or transformed by enemy effects</x:v>
       </x:c>
       <x:c r="J104" s="13" t="str">
-        <x:v>The power of the Sun, in the palm of my hands</x:v>
+        <x:v>Loyalty</x:v>
       </x:c>
       <x:c r="K104" s="13" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Overlord</x:v>
       </x:c>
       <x:c r="L104" s="12" t="str">
-        <x:v>c111</x:v>
+        <x:v>c086</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="42" customHeight="1">
@@ -4757,38 +4757,38 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B110" s="14" t="str">
-        <x:v>Gyoro Gyoro</x:v>
+        <x:v>Gums</x:v>
       </x:c>
       <x:c r="C110" s="23" t="str">
         <x:f>D110&amp;"/"&amp;E110</x:f>
-        <x:v>1/4</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D110" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E110" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F110" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G110" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H110" s="23" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I110" s="13" t="str">
-        <x:v>Ongoing: Give +2/+2 to a friendly Evil minion of your choice</x:v>
+        <x:v>Battlecry: Consume an enemy Nature minion with 4 HP or lower</x:v>
       </x:c>
       <x:c r="J110" s="13" t="str">
-        <x:v>Puppet's puppet-master</x:v>
+        <x:v>Insatiable hunger</x:v>
       </x:c>
       <x:c r="K110" s="13" t="str">
         <x:v>OPM</x:v>
       </x:c>
       <x:c r="L110" s="12" t="str">
-        <x:v>c112</x:v>
+        <x:v>c126</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="42" customHeight="1">
@@ -4796,38 +4796,38 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B111" s="19" t="str">
-        <x:v>Hypnos</x:v>
+        <x:v>Gyoro Gyoro</x:v>
       </x:c>
       <x:c r="C111" s="24" t="str">
         <x:f>D111&amp;"/"&amp;E111</x:f>
-        <x:v>0/5</x:v>
+        <x:v>1/4</x:v>
       </x:c>
       <x:c r="D111" s="22" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E111" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F111" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G111" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H111" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I111" s="18" t="str">
-        <x:v>Taunt. Passive: Enemy minions that attack this become Chained</x:v>
+        <x:v>Ongoing: Give +2/+2 to a friendly Evil minion of your choice</x:v>
       </x:c>
       <x:c r="J111" s="18" t="str">
-        <x:v>He sleeps in his sleep</x:v>
+        <x:v>Puppet's puppet-master</x:v>
       </x:c>
       <x:c r="K111" s="18" t="str">
-        <x:v>Hades</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L111" s="17" t="str">
-        <x:v>c067</x:v>
+        <x:v>c112</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="42" customHeight="1">
@@ -4835,56 +4835,56 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B112" s="14" t="str">
-        <x:v>Kite</x:v>
+        <x:v>Hypnos</x:v>
       </x:c>
       <x:c r="C112" s="23" t="str">
         <x:f>D112&amp;"/"&amp;E112</x:f>
-        <x:v>1/2</x:v>
+        <x:v>0/5</x:v>
       </x:c>
       <x:c r="D112" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E112" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F112" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G112" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H112" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I112" s="13" t="str">
-        <x:v>Ongoing: Roll a dice to gain from +1/+1 to +3/+3</x:v>
+        <x:v>Taunt. Passive: Enemy minions that attack this become Chained</x:v>
       </x:c>
       <x:c r="J112" s="13" t="str">
-        <x:v>Spin the wheel</x:v>
+        <x:v>He sleeps in his sleep</x:v>
       </x:c>
       <x:c r="K112" s="13" t="str">
-        <x:v>HxH</x:v>
+        <x:v>Hades</x:v>
       </x:c>
       <x:c r="L112" s="12" t="str">
-        <x:v>c113</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="60" customHeight="1">
+        <x:v>c067</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="42" customHeight="1">
       <x:c r="A113" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B113" s="19" t="str">
-        <x:v>Lord Voldemort</x:v>
+        <x:v>Kite</x:v>
       </x:c>
       <x:c r="C113" s="24" t="str">
         <x:f>D113&amp;"/"&amp;E113</x:f>
-        <x:v>4/4</x:v>
+        <x:v>1/2</x:v>
       </x:c>
       <x:c r="D113" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E113" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F113" s="24" t="str">
         <x:v>Epic</x:v>
@@ -4893,136 +4893,136 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H113" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I113" s="18" t="str">
-        <x:v>Passive: Any time Voldemort would die, destroy the lowest-HP other friendly minion instead and restore Voldemort to full HP. If he is alone, he dies normally</x:v>
+        <x:v>Ongoing: Roll a dice to gain from +1/+1 to +3/+3</x:v>
       </x:c>
       <x:c r="J113" s="18" t="str">
-        <x:v>Seven horcruxes</x:v>
+        <x:v>Spin the wheel</x:v>
       </x:c>
       <x:c r="K113" s="18" t="str">
-        <x:v>Harry Potter</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L113" s="17" t="str">
-        <x:v>c114</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="44" customHeight="1">
+        <x:v>c113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="60" customHeight="1">
       <x:c r="A114" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B114" s="14" t="str">
-        <x:v>Morpheus</x:v>
+        <x:v>Lord Voldemort</x:v>
       </x:c>
       <x:c r="C114" s="23" t="str">
         <x:f>D114&amp;"/"&amp;E114</x:f>
-        <x:v>2/3</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D114" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E114" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F114" s="23" t="str">
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G114" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H114" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I114" s="13" t="str">
-        <x:v>Battlecry: Discover a random Good or Evil minion from the deck. Draw it</x:v>
+        <x:v>Passive: Any time Voldemort would die, destroy the lowest-HP other friendly minion instead and restore Voldemort to full HP. If he is alone, he dies normally</x:v>
       </x:c>
       <x:c r="J114" s="13" t="str">
-        <x:v>He doesn't offer truth—only the courage to face it</x:v>
+        <x:v>Seven horcruxes</x:v>
       </x:c>
       <x:c r="K114" s="13" t="str">
-        <x:v>Matrix</x:v>
+        <x:v>Harry Potter</x:v>
       </x:c>
       <x:c r="L114" s="12" t="str">
-        <x:v>c054</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="44" customHeight="1">
+        <x:v>c114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="42" customHeight="1">
       <x:c r="A115" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B115" s="19" t="str">
-        <x:v>Motoko Kusanagi</x:v>
+        <x:v>Military Fort</x:v>
       </x:c>
       <x:c r="C115" s="24" t="str">
         <x:f>D115&amp;"/"&amp;E115</x:f>
-        <x:v>2/1</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D115" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E115" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F115" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G115" s="24" t="str">
         <x:v>Tech</x:v>
       </x:c>
       <x:c r="H115" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I115" s="18" t="str">
-        <x:v>Battlecry: Take control of an enemy Tech minion with 4 HP or less until the end of your next turn</x:v>
+        <x:v>Taunt. Cannot attack</x:v>
       </x:c>
       <x:c r="J115" s="18" t="str">
-        <x:v>The ghost can choose the shell.</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K115" s="18" t="str">
-        <x:v>Ghost in the Shell</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L115" s="17" t="str">
-        <x:v>c181</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="42" customHeight="1">
+        <x:v>c103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="44" customHeight="1">
       <x:c r="A116" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B116" s="14" t="str">
-        <x:v>Musashi</x:v>
+        <x:v>Morpheus</x:v>
       </x:c>
       <x:c r="C116" s="23" t="str">
         <x:f>D116&amp;"/"&amp;E116</x:f>
-        <x:v>2/1</x:v>
+        <x:v>2/3</x:v>
       </x:c>
       <x:c r="D116" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E116" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F116" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G116" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H116" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I116" s="13" t="str">
-        <x:v>Battlecry: Destroy all damaged enemy minions</x:v>
+        <x:v>Battlecry: Discover a random Good or Evil minion from the deck. Draw it</x:v>
       </x:c>
       <x:c r="J116" s="13" t="str">
-        <x:v>Another duel to win</x:v>
+        <x:v>He doesn't offer truth—only the courage to face it</x:v>
       </x:c>
       <x:c r="K116" s="13" t="str">
-        <x:v>Baki</x:v>
+        <x:v>Matrix</x:v>
       </x:c>
       <x:c r="L116" s="12" t="str">
-        <x:v>c108</x:v>
+        <x:v>c054</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="44" customHeight="1">
@@ -5030,77 +5030,77 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B117" s="19" t="str">
-        <x:v>Nine Hashira</x:v>
+        <x:v>Motoko Kusanagi</x:v>
       </x:c>
       <x:c r="C117" s="24" t="str">
         <x:f>D117&amp;"/"&amp;E117</x:f>
-        <x:v>3/3</x:v>
+        <x:v>2/1</x:v>
       </x:c>
       <x:c r="D117" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E117" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F117" s="24" t="str">
         <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G117" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H117" s="24" t="str">
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I117" s="18" t="str">
-        <x:v>Battlecry: Choose an enemy Evil minion. Every friendly minion attacks it immediately</x:v>
+        <x:v>Battlecry: Take control of an enemy Tech minion with 4 HP or less until the end of your next turn</x:v>
       </x:c>
       <x:c r="J117" s="18" t="str">
-        <x:v>Nine pillars holding the sky</x:v>
+        <x:v>The ghost can choose the shell.</x:v>
       </x:c>
       <x:c r="K117" s="18" t="str">
-        <x:v>Demon Slayer</x:v>
+        <x:v>Ghost in the Shell</x:v>
       </x:c>
       <x:c r="L117" s="17" t="str">
-        <x:v>c109</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" ht="44" customHeight="1">
+        <x:v>c181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="42" customHeight="1">
       <x:c r="A118" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B118" s="14" t="str">
-        <x:v>Pillar Men</x:v>
+        <x:v>Musashi</x:v>
       </x:c>
       <x:c r="C118" s="23" t="str">
         <x:f>D118&amp;"/"&amp;E118</x:f>
-        <x:v>4/4</x:v>
+        <x:v>2/1</x:v>
       </x:c>
       <x:c r="D118" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E118" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F118" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G118" s="23" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H118" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I118" s="13" t="str">
-        <x:v>Chained. Passive: Whenever Pillar Men kills a minion, restore itself to full health</x:v>
+        <x:v>Battlecry: Destroy all damaged enemy minions</x:v>
       </x:c>
       <x:c r="J118" s="13" t="str">
-        <x:v>They outwaited the sun.</x:v>
+        <x:v>Another duel to win</x:v>
       </x:c>
       <x:c r="K118" s="13" t="str">
-        <x:v>JoJo</x:v>
+        <x:v>Baki</x:v>
       </x:c>
       <x:c r="L118" s="12" t="str">
-        <x:v>c157</x:v>
+        <x:v>c108</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="44" customHeight="1">
@@ -5108,7 +5108,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B119" s="19" t="str">
-        <x:v>Po</x:v>
+        <x:v>Nine Hashira</x:v>
       </x:c>
       <x:c r="C119" s="24" t="str">
         <x:f>D119&amp;"/"&amp;E119</x:f>
@@ -5130,16 +5130,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I119" s="18" t="str">
-        <x:v>Passive: Gain +1/+1 each time you survive after attacking or defending</x:v>
+        <x:v>Battlecry: Choose an enemy Evil minion. Every friendly minion attacks it immediately</x:v>
       </x:c>
       <x:c r="J119" s="18" t="str">
-        <x:v>Chosen by accident. Or destiny?</x:v>
+        <x:v>Nine pillars holding the sky</x:v>
       </x:c>
       <x:c r="K119" s="18" t="str">
-        <x:v>Kung-Fu Panda</x:v>
+        <x:v>Demon Slayer</x:v>
       </x:c>
       <x:c r="L119" s="17" t="str">
-        <x:v>c110</x:v>
+        <x:v>c109</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="42" customHeight="1">
@@ -5147,85 +5147,85 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B120" s="14" t="str">
-        <x:v>Rudeus Greyrat</x:v>
+        <x:v>Nyan</x:v>
       </x:c>
       <x:c r="C120" s="23" t="str">
         <x:f>D120&amp;"/"&amp;E120</x:f>
-        <x:v>2/2</x:v>
+        <x:v>3/1</x:v>
       </x:c>
       <x:c r="D120" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E120" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F120" s="23" t="str">
         <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G120" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H120" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I120" s="13" t="str">
-        <x:v>Divine Shield. Passive: Your Hero Power costs 0</x:v>
+        <x:v>Charge. Passive: Attacks ignore Taunt and cannot be evaded</x:v>
       </x:c>
       <x:c r="J120" s="13" t="str">
-        <x:v>Silent casting, overwhelming force.</x:v>
+        <x:v>Cat King</x:v>
       </x:c>
       <x:c r="K120" s="13" t="str">
-        <x:v>Mushoku Tensei</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L120" s="12" t="str">
-        <x:v>c179</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="42" customHeight="1">
+        <x:v>c127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="44" customHeight="1">
       <x:c r="A121" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B121" s="19" t="str">
-        <x:v>Sans</x:v>
+        <x:v>Pillar Men</x:v>
       </x:c>
       <x:c r="C121" s="24" t="str">
         <x:f>D121&amp;"/"&amp;E121</x:f>
-        <x:v>2/1</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D121" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E121" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F121" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G121" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H121" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I121" s="18" t="str">
-        <x:v>Passive: Evade 80% of attacks</x:v>
+        <x:v>Chained. Passive: Whenever Pillar Men kills a minion, restore itself to full health</x:v>
       </x:c>
       <x:c r="J121" s="18" t="str">
-        <x:v>HELLO, WORLD!</x:v>
+        <x:v>They outwaited the sun.</x:v>
       </x:c>
       <x:c r="K121" s="18" t="str">
-        <x:v>Undertale</x:v>
+        <x:v>JoJo</x:v>
       </x:c>
       <x:c r="L121" s="17" t="str">
-        <x:v>c063</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" ht="42" customHeight="1">
+        <x:v>c157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="44" customHeight="1">
       <x:c r="A122" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B122" s="14" t="str">
-        <x:v>Spider-Man</x:v>
+        <x:v>Po</x:v>
       </x:c>
       <x:c r="C122" s="23" t="str">
         <x:f>D122&amp;"/"&amp;E122</x:f>
@@ -5238,7 +5238,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F122" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G122" s="23" t="str">
         <x:v>Nature</x:v>
@@ -5247,55 +5247,55 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I122" s="13" t="str">
-        <x:v>Battlecry: Freeze an enemy minion and halve its ATK</x:v>
+        <x:v>Passive: Gain +1/+1 each time you survive after attacking or defending</x:v>
       </x:c>
       <x:c r="J122" s="13" t="str">
-        <x:v>Responsibility.</x:v>
+        <x:v>Chosen by accident. Or destiny?</x:v>
       </x:c>
       <x:c r="K122" s="13" t="str">
-        <x:v>MCU</x:v>
+        <x:v>Kung-Fu Panda</x:v>
       </x:c>
       <x:c r="L122" s="12" t="str">
-        <x:v>c035</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="42" customHeight="1">
+        <x:v>c110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="44" customHeight="1">
       <x:c r="A123" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B123" s="19" t="str">
-        <x:v>Wall of Flesh</x:v>
+        <x:v>Ragnaros</x:v>
       </x:c>
       <x:c r="C123" s="24" t="str">
         <x:f>D123&amp;"/"&amp;E123</x:f>
-        <x:v>2/5</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D123" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E123" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F123" s="24" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G123" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H123" s="24" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I123" s="18" t="str">
-        <x:v>Taunt. Ongoing: Deal 1 damage to all other minions</x:v>
+        <x:v>Cannot attack. Ongoing: Deal 3 damage to a random enemy minion or the enemy core</x:v>
       </x:c>
       <x:c r="J123" s="18" t="str">
-        <x:v>A living barricade</x:v>
+        <x:v>Summoned. Once again.</x:v>
       </x:c>
       <x:c r="K123" s="18" t="str">
-        <x:v>Terraria</x:v>
+        <x:v>Hearthstone</x:v>
       </x:c>
       <x:c r="L123" s="17" t="str">
-        <x:v>c122</x:v>
+        <x:v>c031</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="42" customHeight="1">
@@ -5303,77 +5303,77 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B124" s="14" t="str">
-        <x:v>Xenomorph Queen</x:v>
+        <x:v>Rudeus Greyrat</x:v>
       </x:c>
       <x:c r="C124" s="23" t="str">
         <x:f>D124&amp;"/"&amp;E124</x:f>
-        <x:v>1/4</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D124" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E124" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F124" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G124" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H124" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I124" s="13" t="str">
-        <x:v>Passive: Whenever a friendly minion dies summon a 1/1 Larva</x:v>
+        <x:v>Divine Shield. Passive: Your Hero Power costs 0</x:v>
       </x:c>
       <x:c r="J124" s="13" t="str">
-        <x:v>The hive has a mother.</x:v>
+        <x:v>Silent casting, overwhelming force.</x:v>
       </x:c>
       <x:c r="K124" s="13" t="str">
-        <x:v>Alien</x:v>
+        <x:v>Mushoku Tensei</x:v>
       </x:c>
       <x:c r="L124" s="12" t="str">
-        <x:v>c182</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" ht="44" customHeight="1">
+        <x:v>c179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="42" customHeight="1">
       <x:c r="A125" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B125" s="19" t="str">
-        <x:v>Yubaba</x:v>
+        <x:v>Sandworm</x:v>
       </x:c>
       <x:c r="C125" s="24" t="str">
         <x:f>D125&amp;"/"&amp;E125</x:f>
-        <x:v>2/2</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D125" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E125" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F125" s="24" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G125" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H125" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I125" s="18" t="str">
-        <x:v>Battlecry: Devolve your enemy minions into random ones that cost 1 less mana</x:v>
+        <x:v>Taunt. Passive: Cannot be damaged by minions with 3 or less ATK</x:v>
       </x:c>
       <x:c r="J125" s="18" t="str">
-        <x:v>Are you looking for employment?</x:v>
+        <x:v>The desert itself has teeth.</x:v>
       </x:c>
       <x:c r="K125" s="18" t="str">
-        <x:v>Spirited Away</x:v>
+        <x:v>Dune</x:v>
       </x:c>
       <x:c r="L125" s="17" t="str">
-        <x:v>c034</x:v>
+        <x:v>c006</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="42" customHeight="1">
@@ -5381,241 +5381,241 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B126" s="14" t="str">
-        <x:v>Yujiro</x:v>
+        <x:v>Sans</x:v>
       </x:c>
       <x:c r="C126" s="23" t="str">
         <x:f>D126&amp;"/"&amp;E126</x:f>
-        <x:v>4/4</x:v>
+        <x:v>2/1</x:v>
       </x:c>
       <x:c r="D126" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E126" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F126" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G126" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H126" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I126" s="13" t="str">
-        <x:v>Passive: Immune to Nature minions</x:v>
+        <x:v>Passive: Evade 80% of attacks</x:v>
       </x:c>
       <x:c r="J126" s="13" t="str">
-        <x:v>The strongest man alive.</x:v>
+        <x:v>HELLO, WORLD!</x:v>
       </x:c>
       <x:c r="K126" s="13" t="str">
-        <x:v>Baki</x:v>
+        <x:v>Undertale</x:v>
       </x:c>
       <x:c r="L126" s="12" t="str">
-        <x:v>c033</x:v>
+        <x:v>c063</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="42" customHeight="1">
       <x:c r="A127" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B127" s="19" t="str">
-        <x:v>Aizawa</x:v>
+        <x:v>Spider-Man</x:v>
       </x:c>
       <x:c r="C127" s="24" t="str">
         <x:f>D127&amp;"/"&amp;E127</x:f>
-        <x:v>2/2</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D127" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E127" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F127" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G127" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H127" s="24" t="str">
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I127" s="18" t="str">
-        <x:v>Battlecry: Silence an enemy minion of your choice</x:v>
+        <x:v>Battlecry: Freeze an enemy minion and halve its ATK</x:v>
       </x:c>
       <x:c r="J127" s="18" t="str">
-        <x:v>All it takes is one look</x:v>
+        <x:v>Responsibility.</x:v>
       </x:c>
       <x:c r="K127" s="18" t="str">
-        <x:v>MHA</x:v>
+        <x:v>MCU</x:v>
       </x:c>
       <x:c r="L127" s="17" t="str">
-        <x:v>c125</x:v>
+        <x:v>c035</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="42" customHeight="1">
       <x:c r="A128" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B128" s="14" t="str">
-        <x:v>Dabi</x:v>
+        <x:v>Wall of Flesh</x:v>
       </x:c>
       <x:c r="C128" s="23" t="str">
         <x:f>D128&amp;"/"&amp;E128</x:f>
-        <x:v>3/3</x:v>
+        <x:v>2/5</x:v>
       </x:c>
       <x:c r="D128" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E128" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F128" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G128" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H128" s="23" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I128" s="13" t="str">
-        <x:v>Battlecry: Deal 1 damage to all other minions</x:v>
+        <x:v>Taunt. Ongoing: Deal 1 damage to all other minions</x:v>
       </x:c>
       <x:c r="J128" s="13" t="str">
-        <x:v>He burns with anger</x:v>
+        <x:v>A living barricade</x:v>
       </x:c>
       <x:c r="K128" s="13" t="str">
-        <x:v>MHA</x:v>
+        <x:v>Terraria</x:v>
       </x:c>
       <x:c r="L128" s="12" t="str">
-        <x:v>c129</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" ht="44" customHeight="1">
+        <x:v>c122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="42" customHeight="1">
       <x:c r="A129" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B129" s="19" t="str">
-        <x:v>Darkwing</x:v>
+        <x:v>Xenomorph Queen</x:v>
       </x:c>
       <x:c r="C129" s="24" t="str">
         <x:f>D129&amp;"/"&amp;E129</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/4</x:v>
       </x:c>
       <x:c r="D129" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E129" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F129" s="24" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G129" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H129" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I129" s="18" t="str">
-        <x:v>Deathrattle: The minion which kills this minion also dies right after</x:v>
+        <x:v>Passive: Whenever a friendly minion dies summon a 1/1 Larva</x:v>
       </x:c>
       <x:c r="J129" s="18" t="str">
-        <x:v>He knew the cost</x:v>
+        <x:v>The hive has a mother.</x:v>
       </x:c>
       <x:c r="K129" s="18" t="str">
-        <x:v>Invincible</x:v>
+        <x:v>Alien</x:v>
       </x:c>
       <x:c r="L129" s="17" t="str">
-        <x:v>c123</x:v>
+        <x:v>c182</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="44" customHeight="1">
       <x:c r="A130" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B130" s="14" t="str">
-        <x:v>Giant Crystal</x:v>
+        <x:v>Yubaba</x:v>
       </x:c>
       <x:c r="C130" s="23" t="str">
         <x:f>D130&amp;"/"&amp;E130</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D130" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E130" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F130" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G130" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H130" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I130" s="13" t="str">
-        <x:v>Divine Shield. Ongoing: Give all other friendly Magic minions +2/+1</x:v>
+        <x:v>Battlecry: Devolve your enemy minions into random ones that cost 1 less mana</x:v>
       </x:c>
       <x:c r="J130" s="13" t="str">
-        <x:v>Spawnpoint</x:v>
+        <x:v>Are you looking for employment?</x:v>
       </x:c>
       <x:c r="K130" s="13" t="str">
-        <x:v>Core</x:v>
+        <x:v>Spirited Away</x:v>
       </x:c>
       <x:c r="L130" s="12" t="str">
-        <x:v>c137</x:v>
+        <x:v>c034</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="42" customHeight="1">
       <x:c r="A131" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B131" s="19" t="str">
-        <x:v>Giant Tree</x:v>
+        <x:v>Yujiro</x:v>
       </x:c>
       <x:c r="C131" s="24" t="str">
         <x:f>D131&amp;"/"&amp;E131</x:f>
-        <x:v>1/1</x:v>
+        <x:v>4/4</x:v>
       </x:c>
       <x:c r="D131" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E131" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F131" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G131" s="24" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H131" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I131" s="18" t="str">
-        <x:v>Passive: All other friendly Nature minions have +2/+1</x:v>
+        <x:v>Passive: Immune to Nature minions</x:v>
       </x:c>
       <x:c r="J131" s="18" t="str">
-        <x:v>Older than the roots it feeds.</x:v>
+        <x:v>The strongest man alive.</x:v>
       </x:c>
       <x:c r="K131" s="18" t="str">
-        <x:v>Core</x:v>
+        <x:v>Baki</x:v>
       </x:c>
       <x:c r="L131" s="17" t="str">
-        <x:v>c138</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" ht="44" customHeight="1">
+        <x:v>c033</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="42" customHeight="1">
       <x:c r="A132" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B132" s="14" t="str">
-        <x:v>Godrick the Grafted</x:v>
+        <x:v>Aizawa</x:v>
       </x:c>
       <x:c r="C132" s="23" t="str">
         <x:f>D132&amp;"/"&amp;E132</x:f>
@@ -5628,25 +5628,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F132" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G132" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H132" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I132" s="13" t="str">
-        <x:v>Battlecry: Destroy a friendly minion to gain its stats and effects</x:v>
+        <x:v>Battlecry: Silence an enemy minion of your choice</x:v>
       </x:c>
       <x:c r="J132" s="13" t="str">
-        <x:v>Grafted</x:v>
+        <x:v>All it takes is one look</x:v>
       </x:c>
       <x:c r="K132" s="13" t="str">
-        <x:v>Elden Ring</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L132" s="12" t="str">
-        <x:v>c130</x:v>
+        <x:v>c125</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="42" customHeight="1">
@@ -5654,77 +5654,77 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B133" s="19" t="str">
-        <x:v>Gums</x:v>
+        <x:v>Dabi</x:v>
       </x:c>
       <x:c r="C133" s="24" t="str">
         <x:f>D133&amp;"/"&amp;E133</x:f>
-        <x:v>1/1</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D133" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E133" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F133" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G133" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H133" s="24" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I133" s="18" t="str">
-        <x:v>Battlecry: Consume an enemy Nature minion with 4 HP or lower</x:v>
+        <x:v>Battlecry: Deal 1 damage to all other minions</x:v>
       </x:c>
       <x:c r="J133" s="18" t="str">
-        <x:v>Insatiable hunger</x:v>
+        <x:v>He burns with anger</x:v>
       </x:c>
       <x:c r="K133" s="18" t="str">
-        <x:v>OPM</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L133" s="17" t="str">
-        <x:v>c126</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" ht="42" customHeight="1">
+        <x:v>c129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="44" customHeight="1">
       <x:c r="A134" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B134" s="14" t="str">
-        <x:v>Illumi</x:v>
+        <x:v>Darkwing</x:v>
       </x:c>
       <x:c r="C134" s="23" t="str">
         <x:f>D134&amp;"/"&amp;E134</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D134" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E134" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F134" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G134" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H134" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I134" s="13" t="str">
-        <x:v>Battlecry: Gain control of a minion with 2 HP or less</x:v>
+        <x:v>Deathrattle: The minion which kills this minion also dies right after</x:v>
       </x:c>
       <x:c r="J134" s="13" t="str">
-        <x:v>Control</x:v>
+        <x:v>He knew the cost</x:v>
       </x:c>
       <x:c r="K134" s="13" t="str">
-        <x:v>HxH</x:v>
+        <x:v>Invincible</x:v>
       </x:c>
       <x:c r="L134" s="12" t="str">
-        <x:v>c131</x:v>
+        <x:v>c123</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="42" customHeight="1">
@@ -5732,77 +5732,77 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B135" s="19" t="str">
-        <x:v>Kento Nanami</x:v>
+        <x:v>Deep Sea King</x:v>
       </x:c>
       <x:c r="C135" s="24" t="str">
         <x:f>D135&amp;"/"&amp;E135</x:f>
-        <x:v>1/1</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D135" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E135" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F135" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G135" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H135" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I135" s="18" t="str">
-        <x:v>Battlecry: Set an enemy minion's HP to 1</x:v>
+        <x:v>Passive: Costs 3 less while any minion is Frozen or Chained</x:v>
       </x:c>
       <x:c r="J135" s="18" t="str">
-        <x:v>7:3 Ratio Technique</x:v>
+        <x:v>This is why you stay out of the ocean.</x:v>
       </x:c>
       <x:c r="K135" s="18" t="str">
-        <x:v>Jujutsu Kaisen</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L135" s="17" t="str">
-        <x:v>c132</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" ht="60" customHeight="1">
+        <x:v>c039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="42" customHeight="1">
       <x:c r="A136" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B136" s="14" t="str">
-        <x:v>Knov</x:v>
+        <x:v>Eye of Sauron</x:v>
       </x:c>
       <x:c r="C136" s="23" t="str">
         <x:f>D136&amp;"/"&amp;E136</x:f>
-        <x:v>1/1</x:v>
+        <x:v>0/4</x:v>
       </x:c>
       <x:c r="D136" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E136" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F136" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G136" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H136" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I136" s="13" t="str">
-        <x:v>Battlecry: Choose a friendly and an enemy minion to place in the pocket room, removing them from the board. After 2 turns, return the minion with the higher ATK</x:v>
+        <x:v>Passive: Enemy Magic minions cost 2 more</x:v>
       </x:c>
       <x:c r="J136" s="13" t="str">
-        <x:v>The Room</x:v>
+        <x:v>Try and hide.</x:v>
       </x:c>
       <x:c r="K136" s="13" t="str">
-        <x:v>HxH</x:v>
+        <x:v>Lord of the Rings</x:v>
       </x:c>
       <x:c r="L136" s="12" t="str">
-        <x:v>c124</x:v>
+        <x:v>c037</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="44" customHeight="1">
@@ -5810,38 +5810,38 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B137" s="19" t="str">
-        <x:v>Knuckle</x:v>
+        <x:v>Flowey</x:v>
       </x:c>
       <x:c r="C137" s="24" t="str">
         <x:f>D137&amp;"/"&amp;E137</x:f>
-        <x:v>0/3</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D137" s="22" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E137" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F137" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G137" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H137" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I137" s="18" t="str">
-        <x:v>Taunt. Passive: After the enemy minion attacks this minion, it can't attack for 2 turns</x:v>
+        <x:v>Battlecry: Save your core's current HP. Deathrattle: Set your core to the saved HP</x:v>
       </x:c>
       <x:c r="J137" s="18" t="str">
-        <x:v>Taxes</x:v>
+        <x:v>Friendliness is a face you put on.</x:v>
       </x:c>
       <x:c r="K137" s="18" t="str">
-        <x:v>HxH</x:v>
+        <x:v>Undertale</x:v>
       </x:c>
       <x:c r="L137" s="17" t="str">
-        <x:v>c135</x:v>
+        <x:v>c161</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="44" customHeight="1">
@@ -5849,38 +5849,38 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B138" s="14" t="str">
-        <x:v>Kuma</x:v>
+        <x:v>Giant Crystal</x:v>
       </x:c>
       <x:c r="C138" s="23" t="str">
         <x:f>D138&amp;"/"&amp;E138</x:f>
-        <x:v>2/3</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D138" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E138" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F138" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G138" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H138" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I138" s="13" t="str">
-        <x:v>Battlecry: Return a friendly minion to your hand. It costs 5 less the next time it is played this game (minimum 1)</x:v>
+        <x:v>Divine Shield. Ongoing: Give all other friendly Magic minions +2/+1</x:v>
       </x:c>
       <x:c r="J138" s="13" t="str">
-        <x:v>Weapon</x:v>
+        <x:v>Spawnpoint</x:v>
       </x:c>
       <x:c r="K138" s="13" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>Core</x:v>
       </x:c>
       <x:c r="L138" s="12" t="str">
-        <x:v>c133</x:v>
+        <x:v>c137</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="42" customHeight="1">
@@ -5888,77 +5888,77 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B139" s="19" t="str">
-        <x:v>Modern Tank</x:v>
+        <x:v>Giant Tree</x:v>
       </x:c>
       <x:c r="C139" s="24" t="str">
         <x:f>D139&amp;"/"&amp;E139</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D139" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E139" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F139" s="24" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G139" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H139" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I139" s="18" t="str">
-        <x:v>Battlecry: Deal 1 damage to an enemy minion</x:v>
+        <x:v>Passive: All other friendly Nature minions have +2/+1</x:v>
       </x:c>
       <x:c r="J139" s="18" t="str">
-        <x:v>-</x:v>
+        <x:v>Older than the roots it feeds.</x:v>
       </x:c>
       <x:c r="K139" s="18" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Core</x:v>
       </x:c>
       <x:c r="L139" s="17" t="str">
-        <x:v>c139</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" ht="42" customHeight="1">
+        <x:v>c138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="44" customHeight="1">
       <x:c r="A140" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B140" s="14" t="str">
-        <x:v>Morgott, the Omen King</x:v>
+        <x:v>Godrick the Grafted</x:v>
       </x:c>
       <x:c r="C140" s="23" t="str">
         <x:f>D140&amp;"/"&amp;E140</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D140" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E140" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F140" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G140" s="23" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H140" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I140" s="13" t="str">
-        <x:v>Taunt. Battlecry: Summon Margit (1/1 with Taunt)</x:v>
+        <x:v>Battlecry: Destroy a friendly minion to gain its stats and effects</x:v>
       </x:c>
       <x:c r="J140" s="13" t="str">
-        <x:v>The immovable</x:v>
+        <x:v>Grafted</x:v>
       </x:c>
       <x:c r="K140" s="13" t="str">
         <x:v>Elden Ring</x:v>
       </x:c>
       <x:c r="L140" s="12" t="str">
-        <x:v>c155</x:v>
+        <x:v>c130</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="42" customHeight="1">
@@ -5966,38 +5966,38 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B141" s="19" t="str">
-        <x:v>Nyan</x:v>
+        <x:v>Guts</x:v>
       </x:c>
       <x:c r="C141" s="24" t="str">
         <x:f>D141&amp;"/"&amp;E141</x:f>
-        <x:v>3/1</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D141" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E141" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F141" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G141" s="24" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H141" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I141" s="18" t="str">
-        <x:v>Charge. Passive: Ignores Taunt</x:v>
+        <x:v>Passive: Gains +2/+2 for each 20 HP your Core is missing</x:v>
       </x:c>
       <x:c r="J141" s="18" t="str">
-        <x:v>Cat King</x:v>
+        <x:v>Struggle is the only answer.</x:v>
       </x:c>
       <x:c r="K141" s="18" t="str">
-        <x:v>OPM</x:v>
+        <x:v>Berserk</x:v>
       </x:c>
       <x:c r="L141" s="17" t="str">
-        <x:v>c127</x:v>
+        <x:v>c185</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="42" customHeight="1">
@@ -6005,85 +6005,85 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B142" s="14" t="str">
-        <x:v>RoboCop</x:v>
+        <x:v>Illumi</x:v>
       </x:c>
       <x:c r="C142" s="23" t="str">
         <x:f>D142&amp;"/"&amp;E142</x:f>
-        <x:v>2/4</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D142" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E142" s="21" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F142" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G142" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H142" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I142" s="13" t="str">
-        <x:v>Passive: Deal 3x damage against Evil minions</x:v>
+        <x:v>Battlecry: Gain control of a minion with 2 HP or less</x:v>
       </x:c>
       <x:c r="J142" s="13" t="str">
-        <x:v>Uphold the law</x:v>
+        <x:v>Control</x:v>
       </x:c>
       <x:c r="K142" s="13" t="str">
-        <x:v>RoboCop</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L142" s="12" t="str">
-        <x:v>c140</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" ht="44" customHeight="1">
+        <x:v>c131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="42" customHeight="1">
       <x:c r="A143" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B143" s="19" t="str">
-        <x:v>Tai Lung</x:v>
+        <x:v>Kento Nanami</x:v>
       </x:c>
       <x:c r="C143" s="24" t="str">
         <x:f>D143&amp;"/"&amp;E143</x:f>
-        <x:v>3/3</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D143" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E143" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F143" s="24" t="str">
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G143" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H143" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I143" s="18" t="str">
-        <x:v>Chained. Passive: Whenever Tai Lung kills a minion, gain +1/+1 and its keywords</x:v>
+        <x:v>Battlecry: Set an enemy minion's HP to 1</x:v>
       </x:c>
       <x:c r="J143" s="18" t="str">
-        <x:v>Imprisoned for 20 years</x:v>
+        <x:v>7:3 Ratio Technique</x:v>
       </x:c>
       <x:c r="K143" s="18" t="str">
-        <x:v>Kung-Fu Panda</x:v>
+        <x:v>Jujutsu Kaisen</x:v>
       </x:c>
       <x:c r="L143" s="17" t="str">
-        <x:v>c134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" ht="44" customHeight="1">
+        <x:v>c132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="60" customHeight="1">
       <x:c r="A144" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B144" s="14" t="str">
-        <x:v>Tech Hub</x:v>
+        <x:v>Knov</x:v>
       </x:c>
       <x:c r="C144" s="23" t="str">
         <x:f>D144&amp;"/"&amp;E144</x:f>
@@ -6096,199 +6096,199 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F144" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G144" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H144" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I144" s="13" t="str">
-        <x:v>Divine Shield. Ongoing: Give all other friendly Tech minions +2/+1</x:v>
+        <x:v>Battlecry: Choose a friendly and an enemy minion to place in the pocket room, removing them from the board. After 2 turns, return the minion with the higher ATK</x:v>
       </x:c>
       <x:c r="J144" s="13" t="str">
-        <x:v>Every machine came from somewhere. This is that somewhere</x:v>
+        <x:v>The Room</x:v>
       </x:c>
       <x:c r="K144" s="13" t="str">
-        <x:v>Core</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L144" s="12" t="str">
-        <x:v>c141</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" ht="42" customHeight="1">
+        <x:v>c124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="44" customHeight="1">
       <x:c r="A145" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B145" s="19" t="str">
-        <x:v>The Five Convicts</x:v>
+        <x:v>Knuckle</x:v>
       </x:c>
       <x:c r="C145" s="24" t="str">
         <x:f>D145&amp;"/"&amp;E145</x:f>
-        <x:v>5/1</x:v>
+        <x:v>0/3</x:v>
       </x:c>
       <x:c r="D145" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E145" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F145" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G145" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H145" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I145" s="18" t="str">
-        <x:v>Taunt</x:v>
+        <x:v>Taunt. Passive: After the enemy minion attacks this minion, it can't attack for 2 turns</x:v>
       </x:c>
       <x:c r="J145" s="18" t="str">
-        <x:v>death sentence</x:v>
+        <x:v>Taxes</x:v>
       </x:c>
       <x:c r="K145" s="18" t="str">
-        <x:v>Baki</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L145" s="17" t="str">
-        <x:v>c128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" ht="44" customHeight="1">
+        <x:v>c135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="42" customHeight="1">
       <x:c r="A146" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B146" s="14" t="str">
-        <x:v>Yoriichi Type Zero</x:v>
+        <x:v>Lu Bu</x:v>
       </x:c>
       <x:c r="C146" s="23" t="str">
         <x:f>D146&amp;"/"&amp;E146</x:f>
-        <x:v>2/2</x:v>
+        <x:v>3/2</x:v>
       </x:c>
       <x:c r="D146" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E146" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F146" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G146" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H146" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I146" s="13" t="str">
-        <x:v>Passive: Whenever a friendly minion survives a combat, it gains +1/+1</x:v>
+        <x:v>Charge. Lu Bu can only attack the highest-ATK enemy if one exists</x:v>
       </x:c>
       <x:c r="J146" s="13" t="str">
-        <x:v>Strongest puppet</x:v>
+        <x:v>Match any man, then pass him.</x:v>
       </x:c>
       <x:c r="K146" s="13" t="str">
-        <x:v>Demon Slayer</x:v>
+        <x:v>Record of Ragnarok</x:v>
       </x:c>
       <x:c r="L146" s="12" t="str">
-        <x:v>c093</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" ht="44" customHeight="1">
+        <x:v>c149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="42" customHeight="1">
       <x:c r="A147" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B147" s="19" t="str">
-        <x:v>Batman</x:v>
+        <x:v>Modern Tank</x:v>
       </x:c>
       <x:c r="C147" s="24" t="str">
         <x:f>D147&amp;"/"&amp;E147</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D147" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E147" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F147" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G147" s="24" t="str">
         <x:v>Tech</x:v>
       </x:c>
       <x:c r="H147" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I147" s="18" t="str">
-        <x:v>Battlecry: Choose an enemy minion. Choose one gadget: Freeze it; Silence it; or give it -3 ATK</x:v>
+        <x:v>Battlecry: Deal 1 damage to an enemy minion</x:v>
       </x:c>
       <x:c r="J147" s="18" t="str">
-        <x:v>Preparation beats power.</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="K147" s="18" t="str">
-        <x:v>DCEU</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L147" s="17" t="str">
-        <x:v>c005</x:v>
+        <x:v>c139</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="42" customHeight="1">
       <x:c r="A148" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B148" s="14" t="str">
-        <x:v>Bigfoot</x:v>
+        <x:v>Morgott, the Omen King</x:v>
       </x:c>
       <x:c r="C148" s="23" t="str">
         <x:f>D148&amp;"/"&amp;E148</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D148" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E148" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F148" s="23" t="str">
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G148" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H148" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I148" s="13" t="str">
-        <x:v>Passive: Evades 50% of incoming attacks</x:v>
+        <x:v>Taunt. Battlecry: Summon Margit (1/1 with Taunt)</x:v>
       </x:c>
       <x:c r="J148" s="13" t="str">
-        <x:v>The woods answer with silence.</x:v>
+        <x:v>The immovable</x:v>
       </x:c>
       <x:c r="K148" s="13" t="str">
-        <x:v>Myth</x:v>
+        <x:v>Elden Ring</x:v>
       </x:c>
       <x:c r="L148" s="12" t="str">
-        <x:v>c004</x:v>
+        <x:v>c155</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="42" customHeight="1">
       <x:c r="A149" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B149" s="19" t="str">
-        <x:v>Black Ops</x:v>
+        <x:v>RoboCop</x:v>
       </x:c>
       <x:c r="C149" s="24" t="str">
         <x:f>D149&amp;"/"&amp;E149</x:f>
-        <x:v>2/2</x:v>
+        <x:v>2/4</x:v>
       </x:c>
       <x:c r="D149" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E149" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F149" s="24" t="str">
         <x:v>Rare</x:v>
@@ -6297,66 +6297,66 @@
         <x:v>Tech</x:v>
       </x:c>
       <x:c r="H149" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I149" s="18" t="str">
-        <x:v>Passive: Ignore Taunt</x:v>
+        <x:v>Passive: Deal 3x damage against Evil minions</x:v>
       </x:c>
       <x:c r="J149" s="18" t="str">
-        <x:v>Classified</x:v>
+        <x:v>Uphold the law</x:v>
       </x:c>
       <x:c r="K149" s="18" t="str">
-        <x:v>Basic</x:v>
+        <x:v>RoboCop</x:v>
       </x:c>
       <x:c r="L149" s="17" t="str">
-        <x:v>c153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" ht="42" customHeight="1">
+        <x:v>c140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="44" customHeight="1">
       <x:c r="A150" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B150" s="14" t="str">
-        <x:v>Cecil</x:v>
+        <x:v>Tai Lung</x:v>
       </x:c>
       <x:c r="C150" s="23" t="str">
         <x:f>D150&amp;"/"&amp;E150</x:f>
-        <x:v>1/1</x:v>
+        <x:v>3/3</x:v>
       </x:c>
       <x:c r="D150" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E150" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F150" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G150" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H150" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I150" s="13" t="str">
-        <x:v>Battlecry: Return a friendly minion to your hand</x:v>
+        <x:v>Chained. Passive: Whenever Tai Lung kills a minion, gain +1/+1 and its keywords</x:v>
       </x:c>
       <x:c r="J150" s="13" t="str">
-        <x:v>Nothing personal. Just cleanup.</x:v>
+        <x:v>Imprisoned for 20 years</x:v>
       </x:c>
       <x:c r="K150" s="13" t="str">
-        <x:v>Invincible</x:v>
+        <x:v>Kung-Fu Panda</x:v>
       </x:c>
       <x:c r="L150" s="12" t="str">
-        <x:v>c144</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" ht="42" customHeight="1">
+        <x:v>c134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="44" customHeight="1">
       <x:c r="A151" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B151" s="19" t="str">
-        <x:v>Guts</x:v>
+        <x:v>Tech Hub</x:v>
       </x:c>
       <x:c r="C151" s="24" t="str">
         <x:f>D151&amp;"/"&amp;E151</x:f>
@@ -6372,40 +6372,40 @@
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="G151" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H151" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I151" s="18" t="str">
-        <x:v>Passive: Gains +2/+1 for each 20 HP your Core is missing</x:v>
+        <x:v>Divine Shield. Ongoing: Give all other friendly Tech minions +2/+1</x:v>
       </x:c>
       <x:c r="J151" s="18" t="str">
-        <x:v>Struggle is the only answer.</x:v>
+        <x:v>Every machine came from somewhere. This is that somewhere</x:v>
       </x:c>
       <x:c r="K151" s="18" t="str">
-        <x:v>Berserk</x:v>
+        <x:v>Core</x:v>
       </x:c>
       <x:c r="L151" s="17" t="str">
-        <x:v>c185</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" ht="44" customHeight="1">
+        <x:v>c141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="42" customHeight="1">
       <x:c r="A152" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B152" s="14" t="str">
-        <x:v>Kaku Kaioh</x:v>
+        <x:v>The Five Convicts</x:v>
       </x:c>
       <x:c r="C152" s="23" t="str">
         <x:f>D152&amp;"/"&amp;E152</x:f>
-        <x:v>1/2</x:v>
+        <x:v>5/1</x:v>
       </x:c>
       <x:c r="D152" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E152" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F152" s="23" t="str">
         <x:v>Legendary</x:v>
@@ -6414,40 +6414,40 @@
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H152" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I152" s="13" t="str">
-        <x:v>Passive: Evades 50% of attacks. Whenever he evades, the attacker takes damage equal to its own ATK</x:v>
+        <x:v>Taunt</x:v>
       </x:c>
       <x:c r="J152" s="13" t="str">
-        <x:v>162 years old</x:v>
+        <x:v>death sentence</x:v>
       </x:c>
       <x:c r="K152" s="13" t="str">
         <x:v>Baki</x:v>
       </x:c>
       <x:c r="L152" s="12" t="str">
-        <x:v>c145</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" ht="42" customHeight="1">
+        <x:v>c128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="44" customHeight="1">
       <x:c r="A153" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B153" s="19" t="str">
-        <x:v>Kiritsugu Emiya</x:v>
+        <x:v>Yoriichi Type Zero</x:v>
       </x:c>
       <x:c r="C153" s="24" t="str">
         <x:f>D153&amp;"/"&amp;E153</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D153" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E153" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F153" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G153" s="24" t="str">
         <x:v>Tech</x:v>
@@ -6456,16 +6456,16 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I153" s="18" t="str">
-        <x:v>Battlecry: Freeze and silence an enemy minion</x:v>
+        <x:v>Passive: Whenever a friendly minion survives a combat, it gains +1/+1</x:v>
       </x:c>
       <x:c r="J153" s="18" t="str">
-        <x:v>He walks alone</x:v>
+        <x:v>Strongest puppet</x:v>
       </x:c>
       <x:c r="K153" s="18" t="str">
-        <x:v>Fate</x:v>
+        <x:v>Demon Slayer</x:v>
       </x:c>
       <x:c r="L153" s="17" t="str">
-        <x:v>c146</x:v>
+        <x:v>c093</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="44" customHeight="1">
@@ -6473,7 +6473,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B154" s="14" t="str">
-        <x:v>Kureo Mado</x:v>
+        <x:v>Batman</x:v>
       </x:c>
       <x:c r="C154" s="23" t="str">
         <x:f>D154&amp;"/"&amp;E154</x:f>
@@ -6486,25 +6486,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F154" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G154" s="23" t="str">
         <x:v>Tech</x:v>
       </x:c>
       <x:c r="H154" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I154" s="13" t="str">
-        <x:v>Battlecry: Take an enemy minion's Ascension Relic and equip it to Kureo</x:v>
+        <x:v>Battlecry: Choose an enemy minion. Choose one gadget: Freeze it; Silence it; or give it -3 ATK</x:v>
       </x:c>
       <x:c r="J154" s="13" t="str">
-        <x:v>Mad hunter</x:v>
+        <x:v>Preparation beats power.</x:v>
       </x:c>
       <x:c r="K154" s="13" t="str">
-        <x:v>Tokyo Ghoul</x:v>
+        <x:v>DCEU</x:v>
       </x:c>
       <x:c r="L154" s="12" t="str">
-        <x:v>c147</x:v>
+        <x:v>c005</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="42" customHeight="1">
@@ -6512,38 +6512,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B155" s="19" t="str">
-        <x:v>Kurogiri</x:v>
+        <x:v>Bigfoot</x:v>
       </x:c>
       <x:c r="C155" s="24" t="str">
         <x:f>D155&amp;"/"&amp;E155</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D155" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E155" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F155" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G155" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H155" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I155" s="18" t="str">
-        <x:v>Battlecry: All minions attack randomly next turn</x:v>
+        <x:v>Passive: Evades 50% of incoming attacks</x:v>
       </x:c>
       <x:c r="J155" s="18" t="str">
-        <x:v>Every exit leads somewhere else.</x:v>
+        <x:v>The woods answer with silence.</x:v>
       </x:c>
       <x:c r="K155" s="18" t="str">
-        <x:v>MHA</x:v>
+        <x:v>Myth</x:v>
       </x:c>
       <x:c r="L155" s="17" t="str">
-        <x:v>c148</x:v>
+        <x:v>c004</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="42" customHeight="1">
@@ -6551,77 +6551,77 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B156" s="14" t="str">
-        <x:v>Lu Bu</x:v>
+        <x:v>Black Ops</x:v>
       </x:c>
       <x:c r="C156" s="23" t="str">
         <x:f>D156&amp;"/"&amp;E156</x:f>
-        <x:v>2/1</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D156" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E156" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F156" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G156" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H156" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I156" s="13" t="str">
-        <x:v>Charge. Lu Bu can only attack the highest-ATK enemy if one exists</x:v>
+        <x:v>Passive: Ignore Taunt</x:v>
       </x:c>
       <x:c r="J156" s="13" t="str">
-        <x:v>Match any man, then pass him.</x:v>
+        <x:v>Classified</x:v>
       </x:c>
       <x:c r="K156" s="13" t="str">
-        <x:v>Record of Ragnarok</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L156" s="12" t="str">
-        <x:v>c149</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" ht="44" customHeight="1">
+        <x:v>c153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="42" customHeight="1">
       <x:c r="A157" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B157" s="19" t="str">
-        <x:v>Meleoron</x:v>
+        <x:v>Cecil</x:v>
       </x:c>
       <x:c r="C157" s="24" t="str">
         <x:f>D157&amp;"/"&amp;E157</x:f>
-        <x:v>0/1</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D157" s="22" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E157" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F157" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G157" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H157" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I157" s="18" t="str">
-        <x:v>Passive: Choose a friendly minion. It ignores Taunt and cannot be targeted as long as Meleoron is alive</x:v>
+        <x:v>Battlecry: Return a friendly minion to your hand</x:v>
       </x:c>
       <x:c r="J157" s="18" t="str">
-        <x:v>True invisibility</x:v>
+        <x:v>Nothing personal. Just cleanup.</x:v>
       </x:c>
       <x:c r="K157" s="18" t="str">
-        <x:v>HxH</x:v>
+        <x:v>Invincible</x:v>
       </x:c>
       <x:c r="L157" s="17" t="str">
-        <x:v>c150</x:v>
+        <x:v>c144</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="42" customHeight="1">
@@ -6629,14 +6629,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B158" s="14" t="str">
-        <x:v>Mr. Oliva</x:v>
+        <x:v>Dr. Heinz Doofenshmirtz</x:v>
       </x:c>
       <x:c r="C158" s="23" t="str">
         <x:f>D158&amp;"/"&amp;E158</x:f>
-        <x:v>3/2</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D158" s="21" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E158" s="21" t="n">
         <x:v>2</x:v>
@@ -6645,139 +6645,139 @@
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G158" s="23" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H158" s="23" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I158" s="13" t="str">
-        <x:v>Passive: Can only be damaged by ATK of 2 and higher</x:v>
+        <x:v>Ongoing: 50% to die and 50% to double your stats</x:v>
       </x:c>
       <x:c r="J158" s="13" t="str">
-        <x:v>Unchained</x:v>
+        <x:v>Your doom will be unnecessarily complicated</x:v>
       </x:c>
       <x:c r="K158" s="13" t="str">
-        <x:v>Baki</x:v>
+        <x:v>Phineas and Ferb universe</x:v>
       </x:c>
       <x:c r="L158" s="12" t="str">
-        <x:v>c151</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" ht="42" customHeight="1">
+        <x:v>c164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="44" customHeight="1">
       <x:c r="A159" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B159" s="19" t="str">
-        <x:v>Ouken</x:v>
+        <x:v>Kaku Kaioh</x:v>
       </x:c>
       <x:c r="C159" s="24" t="str">
         <x:f>D159&amp;"/"&amp;E159</x:f>
-        <x:v>2/1</x:v>
+        <x:v>1/2</x:v>
       </x:c>
       <x:c r="D159" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E159" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E159" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="F159" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G159" s="24" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H159" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I159" s="18" t="str">
-        <x:v>Reborn infinitely. Become Chained after each Reborn</x:v>
+        <x:v>Passive: Evades 50% of attacks. Whenever he evades, the attacker takes damage equal to its own ATK</x:v>
       </x:c>
       <x:c r="J159" s="18" t="str">
-        <x:v>Immortality cost him everything</x:v>
+        <x:v>162 years old</x:v>
       </x:c>
       <x:c r="K159" s="18" t="str">
-        <x:v>Ranking of Kings</x:v>
+        <x:v>Baki</x:v>
       </x:c>
       <x:c r="L159" s="17" t="str">
-        <x:v>c156</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" ht="44" customHeight="1">
+        <x:v>c145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="42" customHeight="1">
       <x:c r="A160" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B160" s="14" t="str">
-        <x:v>Pandora's Actor</x:v>
+        <x:v>Kiritsugu Emiya</x:v>
       </x:c>
       <x:c r="C160" s="23" t="str">
         <x:f>D160&amp;"/"&amp;E160</x:f>
-        <x:v>2/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D160" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E160" s="21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F160" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G160" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H160" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I160" s="13" t="str">
-        <x:v>Battlecry: Choose another minion. Become it. HP and ATK are not copied</x:v>
+        <x:v>Battlecry: Freeze and silence an enemy minion</x:v>
       </x:c>
       <x:c r="J160" s="13" t="str">
-        <x:v>Every role is useful.</x:v>
+        <x:v>He walks alone</x:v>
       </x:c>
       <x:c r="K160" s="13" t="str">
-        <x:v>Overlord</x:v>
+        <x:v>Fate</x:v>
       </x:c>
       <x:c r="L160" s="12" t="str">
-        <x:v>c007</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" ht="42" customHeight="1">
+        <x:v>c146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="44" customHeight="1">
       <x:c r="A161" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B161" s="19" t="str">
-        <x:v>Sandworm</x:v>
+        <x:v>Kureo Mado</x:v>
       </x:c>
       <x:c r="C161" s="24" t="str">
         <x:f>D161&amp;"/"&amp;E161</x:f>
-        <x:v>1/3</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D161" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E161" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F161" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G161" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Tech</x:v>
       </x:c>
       <x:c r="H161" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I161" s="18" t="str">
-        <x:v>Taunt. Passive: Cannot be damaged by minions with 2 or less ATK</x:v>
+        <x:v>Battlecry: Take an enemy minion's Ascension Relic and equip it to Kureo</x:v>
       </x:c>
       <x:c r="J161" s="18" t="str">
-        <x:v>The desert itself has teeth.</x:v>
+        <x:v>Mad hunter</x:v>
       </x:c>
       <x:c r="K161" s="18" t="str">
-        <x:v>Dune</x:v>
+        <x:v>Tokyo Ghoul</x:v>
       </x:c>
       <x:c r="L161" s="17" t="str">
-        <x:v>c006</x:v>
+        <x:v>c147</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="42" customHeight="1">
@@ -6785,7 +6785,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B162" s="14" t="str">
-        <x:v>Stain</x:v>
+        <x:v>Kurogiri</x:v>
       </x:c>
       <x:c r="C162" s="23" t="str">
         <x:f>D162&amp;"/"&amp;E162</x:f>
@@ -6807,16 +6807,16 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I162" s="13" t="str">
-        <x:v>Battlecry: Destroy a damaged minion</x:v>
+        <x:v>Battlecry: All minions attack randomly next turn</x:v>
       </x:c>
       <x:c r="J162" s="13" t="str">
-        <x:v>No heroes</x:v>
+        <x:v>Every exit leads somewhere else.</x:v>
       </x:c>
       <x:c r="K162" s="13" t="str">
         <x:v>MHA</x:v>
       </x:c>
       <x:c r="L162" s="12" t="str">
-        <x:v>c152</x:v>
+        <x:v>c148</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="44" customHeight="1">
@@ -6824,59 +6824,59 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B163" s="19" t="str">
-        <x:v>Survivors</x:v>
+        <x:v>Meleoron</x:v>
       </x:c>
       <x:c r="C163" s="24" t="str">
         <x:f>D163&amp;"/"&amp;E163</x:f>
-        <x:v>2/2</x:v>
+        <x:v>0/1</x:v>
       </x:c>
       <x:c r="D163" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E163" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F163" s="24" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G163" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H163" s="24" t="str">
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I163" s="18" t="str">
-        <x:v>Divine Shield</x:v>
+        <x:v>Passive: Choose a friendly minion. It ignores Taunt and cannot be targeted as long as Meleoron is alive</x:v>
       </x:c>
       <x:c r="J163" s="18" t="str">
-        <x:v>They weren't the strongest or the fastest. They were the ones who didn't stop</x:v>
+        <x:v>True invisibility</x:v>
       </x:c>
       <x:c r="K163" s="18" t="str">
-        <x:v>L4d2</x:v>
+        <x:v>HxH</x:v>
       </x:c>
       <x:c r="L163" s="17" t="str">
-        <x:v>c143</x:v>
+        <x:v>c150</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="42" customHeight="1">
       <x:c r="A164" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B164" s="14" t="str">
-        <x:v>An Order of Heavy Knights</x:v>
+        <x:v>Mr. Oliva</x:v>
       </x:c>
       <x:c r="C164" s="23" t="str">
         <x:f>D164&amp;"/"&amp;E164</x:f>
-        <x:v>1/1</x:v>
+        <x:v>3/2</x:v>
       </x:c>
       <x:c r="D164" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E164" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F164" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G164" s="23" t="str">
         <x:v>Nature</x:v>
@@ -6885,63 +6885,63 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I164" s="13" t="str">
-        <x:v>Passive: While you control a Taunt minion, this has +1/+1</x:v>
+        <x:v>Passive: Can only be damaged by ATK of 2 and higher</x:v>
       </x:c>
       <x:c r="J164" s="13" t="str">
-        <x:v>Honor. Duty</x:v>
+        <x:v>Unchained</x:v>
       </x:c>
       <x:c r="K164" s="13" t="str">
-        <x:v>Basic</x:v>
+        <x:v>Baki</x:v>
       </x:c>
       <x:c r="L164" s="12" t="str">
-        <x:v>c169</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" ht="44" customHeight="1">
+        <x:v>c151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="42" customHeight="1">
       <x:c r="A165" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B165" s="19" t="str">
-        <x:v>Angstrom Levy</x:v>
+        <x:v>Ouken</x:v>
       </x:c>
       <x:c r="C165" s="24" t="str">
         <x:f>D165&amp;"/"&amp;E165</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/1</x:v>
       </x:c>
       <x:c r="D165" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E165" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F165" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G165" s="24" t="str">
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="H165" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I165" s="18" t="str">
-        <x:v>Battlecry: Choose another minion. Put it on the bottom of the deck and summon a random minion of the same cost into its slot</x:v>
+        <x:v>Reborn infinitely. Become Chained after each Reborn</x:v>
       </x:c>
       <x:c r="J165" s="18" t="str">
-        <x:v>Universe</x:v>
+        <x:v>Immortality cost him everything</x:v>
       </x:c>
       <x:c r="K165" s="18" t="str">
-        <x:v>Invincible</x:v>
+        <x:v>Ranking of Kings</x:v>
       </x:c>
       <x:c r="L165" s="17" t="str">
-        <x:v>c163</x:v>
+        <x:v>c156</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="42" customHeight="1">
       <x:c r="A166" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B166" s="14" t="str">
-        <x:v>Davy Jones</x:v>
+        <x:v>Stain</x:v>
       </x:c>
       <x:c r="C166" s="23" t="str">
         <x:f>D166&amp;"/"&amp;E166</x:f>
@@ -6954,7 +6954,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F166" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G166" s="23" t="str">
         <x:v>Magic</x:v>
@@ -6963,37 +6963,37 @@
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="I166" s="13" t="str">
-        <x:v>Battlecry: Steal an Ascension Relic in your opponent's hand</x:v>
+        <x:v>Battlecry: Destroy a damaged minion</x:v>
       </x:c>
       <x:c r="J166" s="13" t="str">
-        <x:v>Captain of the drowned</x:v>
+        <x:v>No heroes</x:v>
       </x:c>
       <x:c r="K166" s="13" t="str">
-        <x:v>Pirates of the Caribbean</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L166" s="12" t="str">
-        <x:v>c170</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" ht="42" customHeight="1">
+        <x:v>c152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="44" customHeight="1">
       <x:c r="A167" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B167" s="19" t="str">
-        <x:v>Detective L</x:v>
+        <x:v>Survivors</x:v>
       </x:c>
       <x:c r="C167" s="24" t="str">
         <x:f>D167&amp;"/"&amp;E167</x:f>
-        <x:v>1/4</x:v>
+        <x:v>2/2</x:v>
       </x:c>
       <x:c r="D167" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E167" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F167" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G167" s="24" t="str">
         <x:v>Nature</x:v>
@@ -7002,16 +7002,16 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I167" s="18" t="str">
-        <x:v>Passive: Your draw now shows 2 cards, pick one</x:v>
+        <x:v>Divine Shield</x:v>
       </x:c>
       <x:c r="J167" s="18" t="str">
-        <x:v>Justice works in probabilities.</x:v>
+        <x:v>They weren't the strongest or the fastest. They were the ones who didn't stop</x:v>
       </x:c>
       <x:c r="K167" s="18" t="str">
-        <x:v>Death Note</x:v>
+        <x:v>L4d2</x:v>
       </x:c>
       <x:c r="L167" s="17" t="str">
-        <x:v>c003</x:v>
+        <x:v>c143</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="42" customHeight="1">
@@ -7019,7 +7019,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B168" s="14" t="str">
-        <x:v>Domovoy</x:v>
+        <x:v>An Order of Heavy Knights</x:v>
       </x:c>
       <x:c r="C168" s="23" t="str">
         <x:f>D168&amp;"/"&amp;E168</x:f>
@@ -7032,25 +7032,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F168" s="23" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G168" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H168" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I168" s="13" t="str">
-        <x:v>Battlecry: Draw an Ascension Relic</x:v>
+        <x:v>Passive: While you control a Taunt minion, this has +1/+1</x:v>
       </x:c>
       <x:c r="J168" s="13" t="str">
-        <x:v>The house spirit</x:v>
+        <x:v>Honor. Duty</x:v>
       </x:c>
       <x:c r="K168" s="13" t="str">
-        <x:v>Myth</x:v>
+        <x:v>Basic</x:v>
       </x:c>
       <x:c r="L168" s="12" t="str">
-        <x:v>c160</x:v>
+        <x:v>c169</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="42" customHeight="1">
@@ -7058,77 +7058,77 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B169" s="19" t="str">
-        <x:v>Dr. Heinz Doofenshmirtz</x:v>
+        <x:v>Davy Jones</x:v>
       </x:c>
       <x:c r="C169" s="24" t="str">
         <x:f>D169&amp;"/"&amp;E169</x:f>
-        <x:v>1/2</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D169" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E169" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F169" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G169" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H169" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I169" s="18" t="str">
-        <x:v>Ongoing: 50% to die and 50% to gain +2/+1</x:v>
+        <x:v>Battlecry: Steal an Ascension Relic in your opponent's hand</x:v>
       </x:c>
       <x:c r="J169" s="18" t="str">
-        <x:v>Your doom will be unnecessarily complicated</x:v>
+        <x:v>Captain of the drowned</x:v>
       </x:c>
       <x:c r="K169" s="18" t="str">
-        <x:v>Phineas and Ferb universe</x:v>
+        <x:v>Pirates of the Caribbean</x:v>
       </x:c>
       <x:c r="L169" s="17" t="str">
-        <x:v>c164</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" ht="44" customHeight="1">
+        <x:v>c170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="42" customHeight="1">
       <x:c r="A170" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B170" s="14" t="str">
-        <x:v>Flowey</x:v>
+        <x:v>Detective L</x:v>
       </x:c>
       <x:c r="C170" s="23" t="str">
         <x:f>D170&amp;"/"&amp;E170</x:f>
-        <x:v>0/1</x:v>
+        <x:v>1/4</x:v>
       </x:c>
       <x:c r="D170" s="21" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E170" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F170" s="23" t="str">
         <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G170" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H170" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I170" s="13" t="str">
-        <x:v>Battlecry: Save your core's current HP. Deathrattle: Set your core to the saved HP</x:v>
+        <x:v>Passive: Your draw now shows 2 cards, pick one</x:v>
       </x:c>
       <x:c r="J170" s="13" t="str">
-        <x:v>Friendliness is a face you put on.</x:v>
+        <x:v>Justice works in probabilities.</x:v>
       </x:c>
       <x:c r="K170" s="13" t="str">
-        <x:v>Undertale</x:v>
+        <x:v>Death Note</x:v>
       </x:c>
       <x:c r="L170" s="12" t="str">
-        <x:v>c161</x:v>
+        <x:v>c003</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="42" customHeight="1">
@@ -7136,38 +7136,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B171" s="19" t="str">
-        <x:v>Goblins</x:v>
+        <x:v>Domovoy</x:v>
       </x:c>
       <x:c r="C171" s="24" t="str">
         <x:f>D171&amp;"/"&amp;E171</x:f>
-        <x:v>2/1</x:v>
+        <x:v>1/1</x:v>
       </x:c>
       <x:c r="D171" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E171" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F171" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G171" s="24" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H171" s="24" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I171" s="18" t="str">
-        <x:v>Deathrattle: Deal 1 damage to a random enemy minion</x:v>
+        <x:v>Battlecry: Draw an Ascension Relic</x:v>
       </x:c>
       <x:c r="J171" s="18" t="str">
-        <x:v>Many, loud, briefly in the way.</x:v>
+        <x:v>The house spirit</x:v>
       </x:c>
       <x:c r="K171" s="18" t="str">
         <x:v>Myth</x:v>
       </x:c>
       <x:c r="L171" s="17" t="str">
-        <x:v>c171</x:v>
+        <x:v>c160</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="42" customHeight="1">
@@ -7175,38 +7175,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B172" s="14" t="str">
-        <x:v>Indiana Jones</x:v>
+        <x:v>Goblins</x:v>
       </x:c>
       <x:c r="C172" s="23" t="str">
         <x:f>D172&amp;"/"&amp;E172</x:f>
-        <x:v>1/1</x:v>
+        <x:v>2/1</x:v>
       </x:c>
       <x:c r="D172" s="21" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E172" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F172" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G172" s="23" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H172" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I172" s="13" t="str">
-        <x:v>Battlecry: Discover 1 of 3 Ascension Relics. Add it to your hand</x:v>
+        <x:v>Deathrattle: Deal 1 damage to a random enemy minion</x:v>
       </x:c>
       <x:c r="J172" s="13" t="str">
-        <x:v>Mine</x:v>
+        <x:v>Many, loud, briefly in the way.</x:v>
       </x:c>
       <x:c r="K172" s="13" t="str">
-        <x:v>Indiana Jones</x:v>
+        <x:v>Myth</x:v>
       </x:c>
       <x:c r="L172" s="12" t="str">
-        <x:v>c159</x:v>
+        <x:v>c171</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="42" customHeight="1">
@@ -7214,7 +7214,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B173" s="19" t="str">
-        <x:v>John Wick</x:v>
+        <x:v>Indiana Jones</x:v>
       </x:c>
       <x:c r="C173" s="24" t="str">
         <x:f>D173&amp;"/"&amp;E173</x:f>
@@ -7227,25 +7227,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F173" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G173" s="24" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H173" s="24" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I173" s="18" t="str">
-        <x:v>Passive: Whenever a friendly minion dies, gain +1/+1</x:v>
+        <x:v>Battlecry: Discover 1 of 3 Ascension Relics. Add it to your hand</x:v>
       </x:c>
       <x:c r="J173" s="18" t="str">
-        <x:v>A dog was all he had left.</x:v>
+        <x:v>Mine</x:v>
       </x:c>
       <x:c r="K173" s="18" t="str">
-        <x:v>Myth</x:v>
+        <x:v>Indiana Jones</x:v>
       </x:c>
       <x:c r="L173" s="17" t="str">
-        <x:v>c001</x:v>
+        <x:v>c159</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="42" customHeight="1">
@@ -7253,7 +7253,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B174" s="14" t="str">
-        <x:v>Joker</x:v>
+        <x:v>John Wick</x:v>
       </x:c>
       <x:c r="C174" s="23" t="str">
         <x:f>D174&amp;"/"&amp;E174</x:f>
@@ -7266,33 +7266,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F174" s="23" t="str">
-        <x:v>Mythic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G174" s="23" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H174" s="23" t="str">
-        <x:v>Evil</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I174" s="13" t="str">
-        <x:v>Battlecry: Put a copy of a minion in your hand</x:v>
+        <x:v>Passive: Whenever a friendly minion dies, gain +1/+1</x:v>
       </x:c>
       <x:c r="J174" s="13" t="str">
-        <x:v>The punchline was already loaded.</x:v>
+        <x:v>A dog was all he had left.</x:v>
       </x:c>
       <x:c r="K174" s="13" t="str">
-        <x:v>DCU</x:v>
+        <x:v>John Wick</x:v>
       </x:c>
       <x:c r="L174" s="12" t="str">
-        <x:v>c002</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" ht="44" customHeight="1">
+        <x:v>c001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="42" customHeight="1">
       <x:c r="A175" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B175" s="19" t="str">
-        <x:v>Kagaya Ubuyashiki</x:v>
+        <x:v>Joker</x:v>
       </x:c>
       <x:c r="C175" s="24" t="str">
         <x:f>D175&amp;"/"&amp;E175</x:f>
@@ -7305,33 +7305,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F175" s="24" t="str">
-        <x:v>Legendary</x:v>
+        <x:v>Mythic</x:v>
       </x:c>
       <x:c r="G175" s="24" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H175" s="24" t="str">
-        <x:v>Good</x:v>
+        <x:v>Evil</x:v>
       </x:c>
       <x:c r="I175" s="18" t="str">
-        <x:v>Battlecry: Discover a random Taunt, Divine Shield, and Passive minion in the deck. Draw one</x:v>
+        <x:v>Battlecry: Put a copy of a minion in your hand</x:v>
       </x:c>
       <x:c r="J175" s="18" t="str">
-        <x:v>Leadership</x:v>
+        <x:v>The punchline was already loaded.</x:v>
       </x:c>
       <x:c r="K175" s="18" t="str">
-        <x:v>Demon Slayer</x:v>
+        <x:v>DCEU</x:v>
       </x:c>
       <x:c r="L175" s="17" t="str">
-        <x:v>c162</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" ht="42" customHeight="1">
+        <x:v>c002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="44" customHeight="1">
       <x:c r="A176" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B176" s="14" t="str">
-        <x:v>Mr. Poopybutthole</x:v>
+        <x:v>Kagaya Ubuyashiki</x:v>
       </x:c>
       <x:c r="C176" s="23" t="str">
         <x:f>D176&amp;"/"&amp;E176</x:f>
@@ -7344,46 +7344,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F176" s="23" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Legendary</x:v>
       </x:c>
       <x:c r="G176" s="23" t="str">
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H176" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I176" s="13" t="str">
-        <x:v>Reborn</x:v>
+        <x:v>Battlecry: Discover a random Taunt, Divine Shield, and Passive minion in the deck. Draw one</x:v>
       </x:c>
       <x:c r="J176" s="13" t="str">
-        <x:v>He was there the whole time</x:v>
+        <x:v>Leadership</x:v>
       </x:c>
       <x:c r="K176" s="13" t="str">
-        <x:v>Rick and Morty</x:v>
+        <x:v>Demon Slayer</x:v>
       </x:c>
       <x:c r="L176" s="12" t="str">
-        <x:v>c172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" ht="44" customHeight="1">
+        <x:v>c162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="42" customHeight="1">
       <x:c r="A177" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B177" s="19" t="str">
-        <x:v>Mugen &amp; Jin</x:v>
+        <x:v>King</x:v>
       </x:c>
       <x:c r="C177" s="24" t="str">
         <x:f>D177&amp;"/"&amp;E177</x:f>
-        <x:v>1/2</x:v>
+        <x:v>0/5</x:v>
       </x:c>
       <x:c r="D177" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E177" s="22" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F177" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G177" s="24" t="str">
         <x:v>Nature</x:v>
@@ -7392,16 +7392,16 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I177" s="18" t="str">
-        <x:v>Battlecry: Gain +1 ATK if you have another friendly minion on the board</x:v>
+        <x:v>Taunt</x:v>
       </x:c>
       <x:c r="J177" s="18" t="str">
-        <x:v>Two blades, one road, no agreement.</x:v>
+        <x:v>Luckiest man alive</x:v>
       </x:c>
       <x:c r="K177" s="18" t="str">
-        <x:v>Samurai Champloo</x:v>
+        <x:v>OPM</x:v>
       </x:c>
       <x:c r="L177" s="17" t="str">
-        <x:v>c165</x:v>
+        <x:v>c077</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="42" customHeight="1">
@@ -7409,7 +7409,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B178" s="14" t="str">
-        <x:v>Nezu</x:v>
+        <x:v>Mr. Poopybutthole</x:v>
       </x:c>
       <x:c r="C178" s="23" t="str">
         <x:f>D178&amp;"/"&amp;E178</x:f>
@@ -7428,19 +7428,19 @@
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="H178" s="23" t="str">
-        <x:v>Good</x:v>
+        <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I178" s="13" t="str">
-        <x:v>Battlecry: Draw 1 card</x:v>
+        <x:v>Reborn</x:v>
       </x:c>
       <x:c r="J178" s="13" t="str">
-        <x:v>The smartest thing here is a mouse.</x:v>
+        <x:v>He was there the whole time</x:v>
       </x:c>
       <x:c r="K178" s="13" t="str">
-        <x:v>MHA</x:v>
+        <x:v>Rick and Morty</x:v>
       </x:c>
       <x:c r="L178" s="12" t="str">
-        <x:v>c173</x:v>
+        <x:v>c172</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="44" customHeight="1">
@@ -7448,20 +7448,20 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B179" s="19" t="str">
-        <x:v>Shibukawa</x:v>
+        <x:v>Mugen &amp; Jin</x:v>
       </x:c>
       <x:c r="C179" s="24" t="str">
         <x:f>D179&amp;"/"&amp;E179</x:f>
-        <x:v>1/1</x:v>
+        <x:v>1/2</x:v>
       </x:c>
       <x:c r="D179" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E179" s="22" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F179" s="24" t="str">
-        <x:v>Rare</x:v>
+        <x:v>Epic</x:v>
       </x:c>
       <x:c r="G179" s="24" t="str">
         <x:v>Nature</x:v>
@@ -7470,16 +7470,16 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I179" s="18" t="str">
-        <x:v>Divine Shield. Passive: Do 2x damage when defending against an attack</x:v>
+        <x:v>Battlecry: Gain +1 ATK if you have another friendly minion on the board</x:v>
       </x:c>
       <x:c r="J179" s="18" t="str">
-        <x:v>Strength is the easiest thing to redirect.</x:v>
+        <x:v>Two blades, one road, no agreement.</x:v>
       </x:c>
       <x:c r="K179" s="18" t="str">
-        <x:v>Baki</x:v>
+        <x:v>Samurai Champloo</x:v>
       </x:c>
       <x:c r="L179" s="17" t="str">
-        <x:v>c174</x:v>
+        <x:v>c165</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="42" customHeight="1">
@@ -7487,7 +7487,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B180" s="14" t="str">
-        <x:v>Sir Nighteye</x:v>
+        <x:v>Nezu</x:v>
       </x:c>
       <x:c r="C180" s="23" t="str">
         <x:f>D180&amp;"/"&amp;E180</x:f>
@@ -7500,25 +7500,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F180" s="23" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G180" s="23" t="str">
-        <x:v>Magic</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H180" s="23" t="str">
         <x:v>Good</x:v>
       </x:c>
       <x:c r="I180" s="13" t="str">
-        <x:v>Passive: See the card on top of the deck</x:v>
+        <x:v>Battlecry: Draw 1 card</x:v>
       </x:c>
       <x:c r="J180" s="13" t="str">
-        <x:v>He has already watched this end.</x:v>
+        <x:v>The smartest thing here is a mouse.</x:v>
       </x:c>
       <x:c r="K180" s="13" t="str">
         <x:v>MHA</x:v>
       </x:c>
       <x:c r="L180" s="12" t="str">
-        <x:v>c166</x:v>
+        <x:v>c173</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="44" customHeight="1">
@@ -7526,7 +7526,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B181" s="19" t="str">
-        <x:v>V</x:v>
+        <x:v>Shibukawa</x:v>
       </x:c>
       <x:c r="C181" s="24" t="str">
         <x:f>D181&amp;"/"&amp;E181</x:f>
@@ -7548,16 +7548,16 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I181" s="18" t="str">
-        <x:v>Deathrattle: Destroy a random Evil minion, no matter friendly or not, and deal 4 damage to your own Core</x:v>
+        <x:v>Divine Shield. Passive: Do 2x damage when defending against an attack</x:v>
       </x:c>
       <x:c r="J181" s="18" t="str">
-        <x:v>V for Vendetta</x:v>
+        <x:v>Strength is the easiest thing to redirect.</x:v>
       </x:c>
       <x:c r="K181" s="18" t="str">
-        <x:v>V for Vendetta</x:v>
+        <x:v>Baki</x:v>
       </x:c>
       <x:c r="L181" s="17" t="str">
-        <x:v>c175</x:v>
+        <x:v>c174</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="42" customHeight="1">
@@ -7565,7 +7565,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B182" s="14" t="str">
-        <x:v>Vegapunk</x:v>
+        <x:v>Sir Nighteye</x:v>
       </x:c>
       <x:c r="C182" s="23" t="str">
         <x:f>D182&amp;"/"&amp;E182</x:f>
@@ -7581,22 +7581,22 @@
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="G182" s="23" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Magic</x:v>
       </x:c>
       <x:c r="H182" s="23" t="str">
-        <x:v>Neutral</x:v>
+        <x:v>Good</x:v>
       </x:c>
       <x:c r="I182" s="13" t="str">
-        <x:v>Battlecry: Discover 3 Tech cards in the deck, choose and draw one</x:v>
+        <x:v>Passive: See the card on top of the deck</x:v>
       </x:c>
       <x:c r="J182" s="13" t="str">
-        <x:v>His brain never stopped growing</x:v>
+        <x:v>He has already watched this end.</x:v>
       </x:c>
       <x:c r="K182" s="13" t="str">
-        <x:v>One Piece</x:v>
+        <x:v>MHA</x:v>
       </x:c>
       <x:c r="L182" s="12" t="str">
-        <x:v>c167</x:v>
+        <x:v>c166</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="44" customHeight="1">
@@ -7604,7 +7604,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B183" s="19" t="str">
-        <x:v>Walter White</x:v>
+        <x:v>V</x:v>
       </x:c>
       <x:c r="C183" s="24" t="str">
         <x:f>D183&amp;"/"&amp;E183</x:f>
@@ -7617,48 +7617,126 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F183" s="24" t="str">
-        <x:v>Epic</x:v>
+        <x:v>Rare</x:v>
       </x:c>
       <x:c r="G183" s="24" t="str">
-        <x:v>Tech</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="H183" s="24" t="str">
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="I183" s="18" t="str">
+        <x:v>Deathrattle: Destroy a random Evil minion, no matter friendly or not, and deal 4 damage to your own Core</x:v>
+      </x:c>
+      <x:c r="J183" s="18" t="str">
+        <x:v>V for Vendetta</x:v>
+      </x:c>
+      <x:c r="K183" s="18" t="str">
+        <x:v>V for Vendetta</x:v>
+      </x:c>
+      <x:c r="L183" s="17" t="str">
+        <x:v>c175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="42" customHeight="1">
+      <x:c r="A184" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B184" s="14" t="str">
+        <x:v>Vegapunk</x:v>
+      </x:c>
+      <x:c r="C184" s="23" t="str">
+        <x:f>D184&amp;"/"&amp;E184</x:f>
+        <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="D184" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E184" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F184" s="23" t="str">
+        <x:v>Epic</x:v>
+      </x:c>
+      <x:c r="G184" s="23" t="str">
+        <x:v>Tech</x:v>
+      </x:c>
+      <x:c r="H184" s="23" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="I184" s="13" t="str">
+        <x:v>Battlecry: Discover 3 Tech cards in the deck, choose and draw one</x:v>
+      </x:c>
+      <x:c r="J184" s="13" t="str">
+        <x:v>His brain never stopped growing</x:v>
+      </x:c>
+      <x:c r="K184" s="13" t="str">
+        <x:v>One Piece</x:v>
+      </x:c>
+      <x:c r="L184" s="12" t="str">
+        <x:v>c167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="44" customHeight="1">
+      <x:c r="A185" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B185" s="19" t="str">
+        <x:v>Walter White</x:v>
+      </x:c>
+      <x:c r="C185" s="24" t="str">
+        <x:f>D185&amp;"/"&amp;E185</x:f>
+        <x:v>1/1</x:v>
+      </x:c>
+      <x:c r="D185" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E185" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F185" s="24" t="str">
+        <x:v>Epic</x:v>
+      </x:c>
+      <x:c r="G185" s="24" t="str">
+        <x:v>Tech</x:v>
+      </x:c>
+      <x:c r="H185" s="24" t="str">
+        <x:v>Neutral</x:v>
+      </x:c>
+      <x:c r="I185" s="18" t="str">
         <x:v>Battlecry: Choose another friendly Neutral minion. Double its ATK, but set its HP to 1</x:v>
       </x:c>
-      <x:c r="J183" s="18" t="str">
+      <x:c r="J185" s="18" t="str">
         <x:v>Say. My. Name</x:v>
       </x:c>
-      <x:c r="K183" s="18" t="str">
+      <x:c r="K185" s="18" t="str">
         <x:v>Breaking Bad</x:v>
       </x:c>
-      <x:c r="L183" s="17" t="str">
+      <x:c r="L185" s="17" t="str">
         <x:v>c168</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F2:F183">
+  <x:conditionalFormatting sqref="F2:F185">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Rare"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Epic"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Legendary"/>
     <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Mythic"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G2:G183">
+  <x:conditionalFormatting sqref="G2:G185">
     <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Tech"/>
     <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Nature"/>
     <x:cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Magic"/>
     <x:cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="ALL"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="H2:H183">
+  <x:conditionalFormatting sqref="H2:H185">
     <x:cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Good"/>
     <x:cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="Evil"/>
     <x:cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Neutral"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a408c53735046e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc6553008a5b48df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8378,7 +8456,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4d90fcead2b43f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42ac283f91884d9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8495,7 +8573,7 @@
         <x:v>Mythic</x:v>
       </x:c>
       <x:c r="B2" s="8" t="n">
-        <x:f>COUNTIF(Cards!F2:F183,A2)</x:f>
+        <x:f>COUNTIF(Cards!F2:F185,A2)</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="2"/>
@@ -8503,8 +8581,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D2)+COUNTIF(Relics!A2:A35,D2)</x:f>
-        <x:v>11</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D2)+COUNTIF(Relics!A2:A35,D2)</x:f>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
@@ -8512,7 +8590,7 @@
         <x:v>Legendary</x:v>
       </x:c>
       <x:c r="B3" s="8" t="n">
-        <x:f>COUNTIF(Cards!F2:F183,A3)</x:f>
+        <x:f>COUNTIF(Cards!F2:F185,A3)</x:f>
         <x:v>44</x:v>
       </x:c>
       <x:c r="C3" s="2"/>
@@ -8520,7 +8598,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D3)+COUNTIF(Relics!A2:A35,D3)</x:f>
+        <x:f>COUNTIF(Cards!A2:A185,D3)+COUNTIF(Relics!A2:A35,D3)</x:f>
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -8529,7 +8607,7 @@
         <x:v>Epic</x:v>
       </x:c>
       <x:c r="B4" s="8" t="n">
-        <x:f>COUNTIF(Cards!F2:F183,A4)</x:f>
+        <x:f>COUNTIF(Cards!F2:F185,A4)</x:f>
         <x:v>60</x:v>
       </x:c>
       <x:c r="C4" s="2"/>
@@ -8537,8 +8615,8 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D4)+COUNTIF(Relics!A2:A35,D4)</x:f>
-        <x:v>18</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D4)+COUNTIF(Relics!A2:A35,D4)</x:f>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -8546,16 +8624,16 @@
         <x:v>Rare</x:v>
       </x:c>
       <x:c r="B5" s="8" t="n">
-        <x:f>COUNTIF(Cards!F2:F183,A5)</x:f>
-        <x:v>59</x:v>
+        <x:f>COUNTIF(Cards!F2:F185,A5)</x:f>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="2"/>
       <x:c r="D5" s="8" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D5)+COUNTIF(Relics!A2:A35,D5)</x:f>
-        <x:v>18</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D5)+COUNTIF(Relics!A2:A35,D5)</x:f>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -8564,15 +8642,15 @@
       </x:c>
       <x:c r="B6" s="8" t="n">
         <x:f>SUM(B2:B5)</x:f>
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
       <x:c r="D6" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D6)+COUNTIF(Relics!A2:A35,D6)</x:f>
-        <x:v>21</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D6)+COUNTIF(Relics!A2:A35,D6)</x:f>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -8583,8 +8661,8 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D7)+COUNTIF(Relics!A2:A35,D7)</x:f>
-        <x:v>21</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D7)+COUNTIF(Relics!A2:A35,D7)</x:f>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -8597,8 +8675,8 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E8" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D8)+COUNTIF(Relics!A2:A35,D8)</x:f>
-        <x:v>32</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D8)+COUNTIF(Relics!A2:A35,D8)</x:f>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -8606,7 +8684,7 @@
         <x:v>Magic</x:v>
       </x:c>
       <x:c r="B9" s="8" t="n">
-        <x:f>COUNTIF(Cards!G2:G183,A9)</x:f>
+        <x:f>COUNTIF(Cards!G2:G185,A9)</x:f>
         <x:v>89</x:v>
       </x:c>
       <x:c r="C9" s="2"/>
@@ -8614,8 +8692,8 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D9)+COUNTIF(Relics!A2:A35,D9)</x:f>
-        <x:v>27</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D9)+COUNTIF(Relics!A2:A35,D9)</x:f>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
@@ -8623,16 +8701,16 @@
         <x:v>Tech</x:v>
       </x:c>
       <x:c r="B10" s="8" t="n">
-        <x:f>COUNTIF(Cards!G2:G183,A10)</x:f>
-        <x:v>34</x:v>
+        <x:f>COUNTIF(Cards!G2:G185,A10)</x:f>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D10)+COUNTIF(Relics!A2:A35,D10)</x:f>
-        <x:v>26</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D10)+COUNTIF(Relics!A2:A35,D10)</x:f>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
@@ -8640,7 +8718,7 @@
         <x:v>Nature</x:v>
       </x:c>
       <x:c r="B11" s="8" t="n">
-        <x:f>COUNTIF(Cards!G2:G183,A11)</x:f>
+        <x:f>COUNTIF(Cards!G2:G185,A11)</x:f>
         <x:v>57</x:v>
       </x:c>
       <x:c r="C11" s="2"/>
@@ -8648,8 +8726,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="8" t="n">
-        <x:f>COUNTIF(Cards!A2:A183,D11)+COUNTIF(Relics!A2:A35,D11)</x:f>
-        <x:v>30</x:v>
+        <x:f>COUNTIF(Cards!A2:A185,D11)+COUNTIF(Relics!A2:A35,D11)</x:f>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
@@ -8657,7 +8735,7 @@
         <x:v>ALL</x:v>
       </x:c>
       <x:c r="B12" s="8" t="n">
-        <x:f>COUNTIF(Cards!G2:G183,A12)</x:f>
+        <x:f>COUNTIF(Cards!G2:G185,A12)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -8681,7 +8759,7 @@
         <x:v>Good</x:v>
       </x:c>
       <x:c r="E14" s="8" t="n">
-        <x:f>COUNTIF(Cards!H2:H183,D14)</x:f>
+        <x:f>COUNTIF(Cards!H2:H185,D14)</x:f>
         <x:v>56</x:v>
       </x:c>
     </x:row>
@@ -8695,8 +8773,8 @@
         <x:v>Neutral</x:v>
       </x:c>
       <x:c r="E15" s="8" t="n">
-        <x:f>COUNTIF(Cards!H2:H183,D15)</x:f>
-        <x:v>66</x:v>
+        <x:f>COUNTIF(Cards!H2:H185,D15)</x:f>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
@@ -8704,15 +8782,15 @@
         <x:v>Cards</x:v>
       </x:c>
       <x:c r="B16" s="8" t="n">
-        <x:f>COUNTA(Cards!L2:L183)</x:f>
-        <x:v>182</x:v>
+        <x:f>COUNTA(Cards!L2:L185)</x:f>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C16" s="2"/>
       <x:c r="D16" s="2" t="str">
         <x:v>Evil</x:v>
       </x:c>
       <x:c r="E16" s="8" t="n">
-        <x:f>COUNTIF(Cards!H2:H183,D16)</x:f>
+        <x:f>COUNTIF(Cards!H2:H185,D16)</x:f>
         <x:v>60</x:v>
       </x:c>
     </x:row>
@@ -8734,7 +8812,7 @@
       </x:c>
       <x:c r="B18" s="8" t="n">
         <x:f>SUM(B16:B17)</x:f>
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C18" s="2"/>
       <x:c r="D18" s="26" t="str">
